--- a/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/reference_taxa_clusters.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/reference_taxa_clusters.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:R43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>004ABC</t>
+          <t>DR-03</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -581,29 +581,29 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>010B</t>
+          <t>DR-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5385269277308715</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="D3" t="n">
-        <v>5.517161661945792</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E3" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="F3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="G3" t="n">
-        <v>2.874765816126109</v>
+        <v>5.714661819801716</v>
       </c>
       <c r="H3" t="n">
-        <v>5.573081656582537</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I3" t="n">
         <v>3.203426503814917e-16</v>
@@ -615,16 +615,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9297738636749643</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5385269277308715</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.968230419506606</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5385269277308715</v>
+        <v>3.713829095368272</v>
       </c>
       <c r="P3" t="n">
         <v>3.203426503814917e-16</v>
@@ -639,29 +639,29 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>011A</t>
+          <t>DR-54</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>2.010888316142736</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D4" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.025535092107138</v>
       </c>
       <c r="E4" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="F4" t="n">
-        <v>2.010888316142736</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G4" t="n">
-        <v>5.714661819801716</v>
+        <v>4.093511885923145</v>
       </c>
       <c r="H4" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.59778654107874</v>
       </c>
       <c r="I4" t="n">
         <v>3.203426503814917e-16</v>
@@ -676,13 +676,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M4" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.311586150665903</v>
       </c>
       <c r="N4" t="n">
-        <v>4.968230419506606</v>
+        <v>3.025535092107138</v>
       </c>
       <c r="O4" t="n">
-        <v>3.713829095368272</v>
+        <v>5.266786540694901</v>
       </c>
       <c r="P4" t="n">
         <v>3.203426503814917e-16</v>
@@ -697,11 +697,11 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>016C</t>
+          <t>DR-163</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>3.203426503814917e-16</v>
@@ -716,10 +716,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G5" t="n">
-        <v>4.785669732938804</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H5" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.398031073973154</v>
       </c>
       <c r="I5" t="n">
         <v>3.203426503814917e-16</v>
@@ -734,13 +734,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M5" t="n">
-        <v>1.180035029087154</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N5" t="n">
-        <v>5.083698117665277</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O5" t="n">
-        <v>5.330576552960873</v>
+        <v>4.142957953842043</v>
       </c>
       <c r="P5" t="n">
         <v>3.203426503814917e-16</v>
@@ -755,7 +755,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>DR-164</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -765,7 +765,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D6" t="n">
-        <v>3.55019708256048</v>
+        <v>4.045233364735362</v>
       </c>
       <c r="E6" t="n">
         <v>3.203426503814917e-16</v>
@@ -774,10 +774,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.192645077942396</v>
+        <v>1.264986512097531</v>
       </c>
       <c r="H6" t="n">
-        <v>5.988684686772165</v>
+        <v>6.309004397742273</v>
       </c>
       <c r="I6" t="n">
         <v>3.203426503814917e-16</v>
@@ -789,16 +789,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L6" t="n">
-        <v>1.478047296804644</v>
+        <v>1.68511366861321</v>
       </c>
       <c r="M6" t="n">
-        <v>3.025535092107138</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N6" t="n">
-        <v>1.478047296804644</v>
+        <v>0.8579075100879084</v>
       </c>
       <c r="O6" t="n">
-        <v>3.025535092107138</v>
+        <v>1.471200911255877</v>
       </c>
       <c r="P6" t="n">
         <v>3.203426503814917e-16</v>
@@ -807,23 +807,23 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R6" t="n">
-        <v>2.668378508908793</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>DR-167</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D7" t="n">
-        <v>4.045233364735362</v>
+        <v>1.5556469338966</v>
       </c>
       <c r="E7" t="n">
         <v>3.203426503814917e-16</v>
@@ -832,31 +832,31 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.264986512097531</v>
+        <v>5.635374126367335</v>
       </c>
       <c r="H7" t="n">
-        <v>6.309004397742273</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I7" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J7" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.76955288934522</v>
       </c>
       <c r="K7" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7194478329081769</v>
       </c>
       <c r="L7" t="n">
-        <v>1.68511366861321</v>
+        <v>1.197301440373618</v>
       </c>
       <c r="M7" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8969065070358966</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8579075100879084</v>
+        <v>0.5170584362193528</v>
       </c>
       <c r="O7" t="n">
-        <v>1.471200911255877</v>
+        <v>5.368130103004817</v>
       </c>
       <c r="P7" t="n">
         <v>3.203426503814917e-16</v>
@@ -871,17 +871,17 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>DR-168</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5556469338966</v>
+        <v>5.881934108295542</v>
       </c>
       <c r="E8" t="n">
         <v>3.203426503814917e-16</v>
@@ -890,31 +890,31 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G8" t="n">
-        <v>5.635374126367335</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H8" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.273559133363798</v>
       </c>
       <c r="I8" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J8" t="n">
-        <v>2.76955288934522</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7194478329081769</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L8" t="n">
-        <v>1.197301440373618</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8969065070358966</v>
+        <v>1.292354979504015</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5170584362193528</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O8" t="n">
-        <v>5.368130103004817</v>
+        <v>1.962937905778455</v>
       </c>
       <c r="P8" t="n">
         <v>3.203426503814917e-16</v>
@@ -929,17 +929,17 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>DR-175</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D9" t="n">
-        <v>3.934112064343543</v>
+        <v>1.745427172914403</v>
       </c>
       <c r="E9" t="n">
         <v>3.203426503814917e-16</v>
@@ -948,10 +948,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.526545814495834</v>
+        <v>4.126856279550426</v>
       </c>
       <c r="H9" t="n">
-        <v>6.13026410847607</v>
+        <v>2.179323699444562</v>
       </c>
       <c r="I9" t="n">
         <v>3.203426503814917e-16</v>
@@ -966,13 +966,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M9" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.121990524378611</v>
       </c>
       <c r="N9" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.121990524378611</v>
       </c>
       <c r="O9" t="n">
-        <v>3.689831618575111</v>
+        <v>6.25349992300136</v>
       </c>
       <c r="P9" t="n">
         <v>3.203426503814917e-16</v>
@@ -987,26 +987,26 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>DR-195</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="D10" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="E10" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.721932779208732</v>
       </c>
       <c r="F10" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G10" t="n">
-        <v>6.438197784198078</v>
+        <v>6.304671300699757</v>
       </c>
       <c r="H10" t="n">
         <v>3.203426503814917e-16</v>
@@ -1021,16 +1021,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L10" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="M10" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N10" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.827323338290201</v>
       </c>
       <c r="O10" t="n">
-        <v>3.934112064343543</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P10" t="n">
         <v>3.203426503814917e-16</v>
@@ -1045,17 +1045,17 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>DR-197</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9047272710591775</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E11" t="n">
         <v>3.203426503814917e-16</v>
@@ -1064,10 +1064,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09368399654834478</v>
+        <v>6.051070184214275</v>
       </c>
       <c r="H11" t="n">
-        <v>6.643280158288579</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I11" t="n">
         <v>3.203426503814917e-16</v>
@@ -1079,16 +1079,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09368399654834478</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M11" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N11" t="n">
-        <v>0.04760230704818257</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O11" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.157604729806445</v>
       </c>
       <c r="P11" t="n">
         <v>3.203426503814917e-16</v>
@@ -1103,11 +1103,11 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>DR-202</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
         <v>3.203426503814917e-16</v>
@@ -1125,7 +1125,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="H12" t="n">
-        <v>6.643254941572279</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I12" t="n">
         <v>3.203426503814917e-16</v>
@@ -1146,7 +1146,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="O12" t="n">
-        <v>1.029747343394052</v>
+        <v>6.658211482751795</v>
       </c>
       <c r="P12" t="n">
         <v>3.203426503814917e-16</v>
@@ -1161,29 +1161,29 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>DR-204</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>1.611075341040287</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D13" t="n">
-        <v>1.611075341040287</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E13" t="n">
-        <v>5.02267182631393</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F13" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G13" t="n">
-        <v>5.887992562015887</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.357552004618084</v>
       </c>
       <c r="I13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1192,19 +1192,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7526899464592227</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L13" t="n">
-        <v>1.611075341040287</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M13" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N13" t="n">
-        <v>1.244803668756707</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O13" t="n">
-        <v>1.611075341040287</v>
+        <v>5.930737337562887</v>
       </c>
       <c r="P13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1219,32 +1219,32 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>DR-205</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>1.150242635580613</v>
+        <v>0.7649411668273915</v>
       </c>
       <c r="D14" t="n">
-        <v>1.150242635580613</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E14" t="n">
-        <v>3.721932779208732</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F14" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G14" t="n">
-        <v>6.304671300699757</v>
+        <v>0.2324460860003711</v>
       </c>
       <c r="H14" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I14" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.2324460860003711</v>
       </c>
       <c r="J14" t="n">
         <v>3.203426503814917e-16</v>
@@ -1253,16 +1253,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L14" t="n">
-        <v>1.150242635580613</v>
+        <v>0.2324460860003711</v>
       </c>
       <c r="M14" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N14" t="n">
-        <v>2.827323338290201</v>
+        <v>0.7649411668273915</v>
       </c>
       <c r="O14" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.630477159973525</v>
       </c>
       <c r="P14" t="n">
         <v>3.203426503814917e-16</v>
@@ -1277,14 +1277,14 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>DR-206</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.605196984461211</v>
       </c>
       <c r="D15" t="n">
         <v>3.203426503814917e-16</v>
@@ -1296,7 +1296,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G15" t="n">
-        <v>6.051070184214275</v>
+        <v>3.244061423481349</v>
       </c>
       <c r="H15" t="n">
         <v>3.203426503814917e-16</v>
@@ -1317,10 +1317,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.64825093183208</v>
       </c>
       <c r="O15" t="n">
-        <v>5.157604729806445</v>
+        <v>5.258825506031243</v>
       </c>
       <c r="P15" t="n">
         <v>3.203426503814917e-16</v>
@@ -1335,29 +1335,29 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>071B</t>
+          <t>DR-207</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.200819009388096</v>
       </c>
       <c r="E16" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="F16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.200819009388096</v>
       </c>
       <c r="G16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.291634172573763</v>
       </c>
       <c r="H16" t="n">
-        <v>6.339850002884624</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I16" t="n">
         <v>3.203426503814917e-16</v>
@@ -1375,10 +1375,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.334984247712808</v>
       </c>
       <c r="O16" t="n">
-        <v>4.392317422778761</v>
+        <v>6.416427414239525</v>
       </c>
       <c r="P16" t="n">
         <v>3.203426503814917e-16</v>
@@ -1393,11 +1393,11 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>DR-208</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1412,7 +1412,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.343954401217361</v>
       </c>
       <c r="H17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1433,10 +1433,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.027480736422107</v>
       </c>
       <c r="O17" t="n">
-        <v>6.658211482751795</v>
+        <v>6.590730981180768</v>
       </c>
       <c r="P17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1451,17 +1451,17 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>094C</t>
+          <t>DR-209</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E18" t="n">
         <v>3.203426503814917e-16</v>
@@ -1473,7 +1473,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="H18" t="n">
-        <v>6.426264754702098</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I18" t="n">
         <v>3.203426503814917e-16</v>
@@ -1485,16 +1485,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.902932582039835</v>
       </c>
       <c r="M18" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.244803668756707</v>
       </c>
       <c r="O18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.598281987085227</v>
       </c>
       <c r="P18" t="n">
         <v>3.203426503814917e-16</v>
@@ -1509,38 +1509,38 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>DR-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1.529467388129453</v>
+        <v>0.7907111659377324</v>
       </c>
       <c r="D19" t="n">
-        <v>4.776898533069642</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7907111659377324</v>
       </c>
       <c r="F19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G19" t="n">
-        <v>3.623018726983232</v>
+        <v>4.372118352313833</v>
       </c>
       <c r="H19" t="n">
-        <v>2.255073120131111</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.970746195024886</v>
       </c>
       <c r="J19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7907111659377324</v>
       </c>
       <c r="L19" t="n">
         <v>3.203426503814917e-16</v>
@@ -1549,10 +1549,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N19" t="n">
-        <v>5.203555779323592</v>
+        <v>4.881035788519983</v>
       </c>
       <c r="O19" t="n">
-        <v>4.443256343088573</v>
+        <v>5.576380898876536</v>
       </c>
       <c r="P19" t="n">
         <v>3.203426503814917e-16</v>
@@ -1567,11 +1567,11 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>DR-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
         <v>3.203426503814917e-16</v>
@@ -1586,7 +1586,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G20" t="n">
-        <v>4.886132035441721</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H20" t="n">
         <v>3.203426503814917e-16</v>
@@ -1595,7 +1595,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J20" t="n">
-        <v>2.345292087952873</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K20" t="n">
         <v>3.203426503814917e-16</v>
@@ -1607,10 +1607,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N20" t="n">
-        <v>5.861530062208643</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48595249488999</v>
+        <v>6.658211482751795</v>
       </c>
       <c r="P20" t="n">
         <v>3.203426503814917e-16</v>
@@ -1625,50 +1625,50 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>DR-18</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6716424538336574</v>
       </c>
       <c r="D21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.128142095540397</v>
       </c>
       <c r="E21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6716424538336574</v>
       </c>
       <c r="F21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6716424538336574</v>
       </c>
       <c r="G21" t="n">
-        <v>4.402534852460246</v>
+        <v>6.148943747704833</v>
       </c>
       <c r="H21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8403736653519254</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8042755291256324</v>
+        <v>0.260180408778641</v>
       </c>
       <c r="J21" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.4805307985768705</v>
       </c>
       <c r="L21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.4805307985768705</v>
       </c>
       <c r="M21" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N21" t="n">
-        <v>6.289812447870645</v>
+        <v>1.666262602823005</v>
       </c>
       <c r="O21" t="n">
-        <v>1.518873310263384</v>
+        <v>4.592309300379081</v>
       </c>
       <c r="P21" t="n">
         <v>3.203426503814917e-16</v>
@@ -1683,17 +1683,17 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>DR-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D22" t="n">
-        <v>3.582027209696609</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E22" t="n">
         <v>3.203426503814917e-16</v>
@@ -1702,10 +1702,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6868421147403698</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H22" t="n">
-        <v>6.452617933046574</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I22" t="n">
         <v>3.203426503814917e-16</v>
@@ -1723,10 +1723,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N22" t="n">
-        <v>1.150242635580613</v>
+        <v>0.795180208111502</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6868421147403698</v>
+        <v>6.647670042889607</v>
       </c>
       <c r="P22" t="n">
         <v>3.203426503814917e-16</v>
@@ -1741,32 +1741,32 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>DR-20</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>0.399421886369236</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D23" t="n">
-        <v>4.441858732844736</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E23" t="n">
-        <v>0.399421886369236</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F23" t="n">
-        <v>0.399421886369236</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G23" t="n">
-        <v>4.592516646115072</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H23" t="n">
-        <v>4.3657782510295</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I23" t="n">
-        <v>1.186447986673725</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1775,16 +1775,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9685979008608663</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N23" t="n">
-        <v>3.28864350317529</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O23" t="n">
-        <v>4.648634242809477</v>
+        <v>6.658211482751795</v>
       </c>
       <c r="P23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1793,32 +1793,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5641038958234921</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>DR-23</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.813821517558835</v>
       </c>
       <c r="D24" t="n">
-        <v>2.345292087952873</v>
+        <v>0.9585800726200192</v>
       </c>
       <c r="E24" t="n">
-        <v>3.195861790625938</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F24" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G24" t="n">
-        <v>3.934112064343543</v>
+        <v>2.926715573964768</v>
       </c>
       <c r="H24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1830,7 +1830,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3944761767965276</v>
       </c>
       <c r="L24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1839,10 +1839,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N24" t="n">
-        <v>2.345292087952873</v>
+        <v>2.255073120131111</v>
       </c>
       <c r="O24" t="n">
-        <v>6.137252569345645</v>
+        <v>6.440438272660687</v>
       </c>
       <c r="P24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1857,84 +1857,84 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>DR-38</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>1.330645311988472</v>
+        <v>0.399421886369236</v>
       </c>
       <c r="D25" t="n">
-        <v>3.713829095368272</v>
+        <v>4.441858732844736</v>
       </c>
       <c r="E25" t="n">
-        <v>2.010888316142736</v>
+        <v>0.399421886369236</v>
       </c>
       <c r="F25" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.399421886369236</v>
       </c>
       <c r="G25" t="n">
-        <v>5.036423408249874</v>
+        <v>4.592516646115072</v>
       </c>
       <c r="H25" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.3657782510295</v>
       </c>
       <c r="I25" t="n">
-        <v>3.100264123473429</v>
+        <v>1.186447986673725</v>
       </c>
       <c r="J25" t="n">
-        <v>4.896653486982127</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K25" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L25" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9685979008608663</v>
       </c>
       <c r="M25" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>2.010888316142736</v>
+        <v>3.28864350317529</v>
       </c>
       <c r="O25" t="n">
-        <v>3.334984247712809</v>
+        <v>4.648634242809477</v>
       </c>
       <c r="P25" t="n">
-        <v>2.010888316142736</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q25" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R25" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5641038958234921</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>DR-40</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.438263439136034</v>
       </c>
       <c r="D26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.911665100928866</v>
       </c>
       <c r="E26" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="F26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.073801300410117</v>
       </c>
       <c r="G26" t="n">
-        <v>5.672425341971495</v>
+        <v>4.223388413810172</v>
       </c>
       <c r="H26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1949,16 +1949,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6345804331377208</v>
       </c>
       <c r="M26" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N26" t="n">
-        <v>2.584962500721157</v>
+        <v>4.629759124069301</v>
       </c>
       <c r="O26" t="n">
-        <v>5.523561956057013</v>
+        <v>5.648789573465464</v>
       </c>
       <c r="P26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1967,20 +1967,20 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6345804331377208</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>DR-44</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>1.350716518311987</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D27" t="n">
         <v>3.203426503814917e-16</v>
@@ -1992,7 +1992,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G27" t="n">
-        <v>5.350259665639975</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="H27" t="n">
         <v>3.203426503814917e-16</v>
@@ -2010,56 +2010,56 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M27" t="n">
-        <v>0.331588205937932</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N27" t="n">
-        <v>1.196600538156653</v>
+        <v>5.101538026462062</v>
       </c>
       <c r="O27" t="n">
-        <v>5.78825675019676</v>
+        <v>6.014274130982118</v>
       </c>
       <c r="P27" t="n">
-        <v>1.024030069363076</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.331588205937932</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R27" t="n">
-        <v>1.350716518311987</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>DR-45</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>1.908283830908385</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1952562913989341</v>
+        <v>2.345292087952873</v>
       </c>
       <c r="E28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.195861790625938</v>
       </c>
       <c r="F28" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G28" t="n">
-        <v>5.392815161283227</v>
+        <v>3.934112064343543</v>
       </c>
       <c r="H28" t="n">
-        <v>1.52810016376548</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5208321633014408</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9027027986450852</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K28" t="n">
         <v>3.203426503814917e-16</v>
@@ -2068,53 +2068,53 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3672089741882289</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N28" t="n">
-        <v>1.375291320486087</v>
+        <v>2.345292087952873</v>
       </c>
       <c r="O28" t="n">
-        <v>5.626608427361777</v>
+        <v>6.137252569345645</v>
       </c>
       <c r="P28" t="n">
-        <v>1.110644063683993</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.204358498506187</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1952562913989341</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>DR-48</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9928402084271342</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5801932565732844</v>
+        <v>0.4378774756369554</v>
       </c>
       <c r="F29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G29" t="n">
-        <v>4.07395594291159</v>
+        <v>1.045323990509491</v>
       </c>
       <c r="H29" t="n">
-        <v>2.158772140503586</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I29" t="n">
-        <v>3.235090048108769</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J29" t="n">
         <v>3.203426503814917e-16</v>
@@ -2126,19 +2126,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M29" t="n">
-        <v>1.797115737552766</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.745382295550968</v>
       </c>
       <c r="O29" t="n">
-        <v>5.963153611563069</v>
+        <v>6.445763325802663</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5801932565732844</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.894457614762477</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R29" t="n">
         <v>3.203426503814917e-16</v>
@@ -2147,26 +2147,26 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>DR-49</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3263154121283017</v>
+        <v>1.357552004618084</v>
       </c>
       <c r="D30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E30" t="n">
-        <v>0.08875461424297566</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F30" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.357552004618084</v>
       </c>
       <c r="G30" t="n">
-        <v>5.998740754099797</v>
+        <v>2.857980995127572</v>
       </c>
       <c r="H30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2184,19 +2184,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6517437797578886</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N30" t="n">
-        <v>1.473345203336181</v>
+        <v>5.988684686772165</v>
       </c>
       <c r="O30" t="n">
-        <v>5.142716125671646</v>
+        <v>4.864186144654281</v>
       </c>
       <c r="P30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.08875461424297566</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2205,32 +2205,32 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>DR-50</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.769618811484958</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F31" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G31" t="n">
-        <v>5.144054104230877</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H31" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J31" t="n">
         <v>3.203426503814917e-16</v>
@@ -2239,22 +2239,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L31" t="n">
-        <v>1.85065345479636</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M31" t="n">
-        <v>1.127523751722153</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N31" t="n">
-        <v>1.410757771901608</v>
+        <v>5.584600333017261</v>
       </c>
       <c r="O31" t="n">
-        <v>5.889810299081591</v>
+        <v>5.689366530544118</v>
       </c>
       <c r="P31" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R31" t="n">
         <v>3.203426503814917e-16</v>
@@ -2263,26 +2263,26 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>DR-51</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4989892776113035</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D32" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8690393221168372</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F32" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G32" t="n">
-        <v>5.38919132179204</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H32" t="n">
         <v>3.203426503814917e-16</v>
@@ -2303,10 +2303,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N32" t="n">
-        <v>1.163285804079277</v>
+        <v>2.646890249864358</v>
       </c>
       <c r="O32" t="n">
-        <v>5.848286675010258</v>
+        <v>6.5810023142079</v>
       </c>
       <c r="P32" t="n">
         <v>3.203426503814917e-16</v>
@@ -2321,17 +2321,17 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>DR-53</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D33" t="n">
-        <v>1.888578717331577</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E33" t="n">
         <v>3.203426503814917e-16</v>
@@ -2340,14 +2340,14 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G33" t="n">
-        <v>4.662451872030237</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H33" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I33" t="n">
         <v>0.7447429447579256</v>
       </c>
-      <c r="I33" t="n">
-        <v>1.597901556428655</v>
-      </c>
       <c r="J33" t="n">
         <v>3.203426503814917e-16</v>
       </c>
@@ -2361,53 +2361,53 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N33" t="n">
-        <v>1.888578717331577</v>
+        <v>3.075948853233299</v>
       </c>
       <c r="O33" t="n">
-        <v>6.056161680855508</v>
+        <v>6.537480770743348</v>
       </c>
       <c r="P33" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.233490130219779</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R33" t="n">
-        <v>0.7447429447579256</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>DR-55</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8654578766211725</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E34" t="n">
-        <v>1.067563283812635</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F34" t="n">
-        <v>1.902932582039835</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G34" t="n">
-        <v>4.254154983721236</v>
+        <v>2.206161150578032</v>
       </c>
       <c r="H34" t="n">
-        <v>5.183584401348678</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I34" t="n">
-        <v>3.022063735665987</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J34" t="n">
-        <v>2.695871814459378</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K34" t="n">
         <v>3.203426503814917e-16</v>
@@ -2419,25 +2419,25 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N34" t="n">
-        <v>2.273699814391163</v>
+        <v>3.566008174993656</v>
       </c>
       <c r="O34" t="n">
-        <v>4.42947839653567</v>
+        <v>6.435331368836803</v>
       </c>
       <c r="P34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.273699814391163</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R34" t="n">
-        <v>1.067563283812635</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>DR-56</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2456,7 +2456,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G35" t="n">
-        <v>6.131155431277737</v>
+        <v>2.584962500721157</v>
       </c>
       <c r="H35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2471,7 +2471,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L35" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.584962500721157</v>
       </c>
       <c r="M35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2480,7 +2480,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="O35" t="n">
-        <v>4.995895601667264</v>
+        <v>6.507794640198696</v>
       </c>
       <c r="P35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2495,32 +2495,32 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>DR-59</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>1.304854581528421</v>
+        <v>0.82797653267369</v>
       </c>
       <c r="D36" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E36" t="n">
-        <v>2.584962500721157</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F36" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G36" t="n">
-        <v>6.082462160191973</v>
+        <v>1.350716518311988</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6674246609131292</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3719687773869582</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2535,16 +2535,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N36" t="n">
-        <v>1.745427172914402</v>
+        <v>2.285688951456035</v>
       </c>
       <c r="O36" t="n">
-        <v>4.527247002864868</v>
+        <v>6.56679155955111</v>
       </c>
       <c r="P36" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.304854581528421</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2553,32 +2553,32 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7015976723254892</v>
       </c>
       <c r="D37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.318611206510286</v>
       </c>
       <c r="E37" t="n">
-        <v>2.508772937544713</v>
+        <v>2.775158340656881</v>
       </c>
       <c r="F37" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G37" t="n">
-        <v>5.871125674841771</v>
+        <v>5.172850259602431</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3183614798671702</v>
+        <v>1.720913610124057</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7997013495141689</v>
+        <v>3.801534553146519</v>
       </c>
       <c r="J37" t="n">
         <v>3.203426503814917e-16</v>
@@ -2590,32 +2590,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7997013495141689</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.80950466920085</v>
       </c>
       <c r="O37" t="n">
-        <v>5.172396639944554</v>
+        <v>4.976371289815223</v>
       </c>
       <c r="P37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7015976723254892</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9910668752299923</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7015976723254892</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>DR-140</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2627,19 +2627,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="F38" t="n">
-        <v>0.540568381362703</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G38" t="n">
-        <v>5.853451336647058</v>
+        <v>3.225220681487266</v>
       </c>
       <c r="H38" t="n">
-        <v>0.540568381362703</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I38" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J38" t="n">
-        <v>2.212993723334198</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2651,50 +2651,50 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N38" t="n">
-        <v>2.740240726199067</v>
+        <v>4.82031925463496</v>
       </c>
       <c r="O38" t="n">
-        <v>5.056268219646745</v>
+        <v>6.021391865052195</v>
       </c>
       <c r="P38" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.540568381362703</v>
+        <v>0.525628361338754</v>
       </c>
       <c r="R38" t="n">
-        <v>0.2954558835261716</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="D39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="F39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G39" t="n">
-        <v>6.086383652788929</v>
+        <v>5.144054104230877</v>
       </c>
       <c r="H39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I39" t="n">
-        <v>2.501061243112211</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="J39" t="n">
         <v>3.203426503814917e-16</v>
@@ -2703,38 +2703,38 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.85065345479636</v>
       </c>
       <c r="M39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.127523751722153</v>
       </c>
       <c r="N39" t="n">
-        <v>2.267104070142841</v>
+        <v>1.410757771901608</v>
       </c>
       <c r="O39" t="n">
-        <v>4.52568669140555</v>
+        <v>5.889810299081591</v>
       </c>
       <c r="P39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.430239905922514</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="R39" t="n">
-        <v>0.8855412754150851</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>3.598259323334614</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D40" t="n">
         <v>3.203426503814917e-16</v>
@@ -2746,7 +2746,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G40" t="n">
-        <v>3.598259323334614</v>
+        <v>6.131155431277737</v>
       </c>
       <c r="H40" t="n">
         <v>3.203426503814917e-16</v>
@@ -2767,16 +2767,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N40" t="n">
-        <v>3.598259323334614</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O40" t="n">
-        <v>4.53743413063857</v>
+        <v>4.995895601667264</v>
       </c>
       <c r="P40" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.506032031499436</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R40" t="n">
         <v>3.203426503814917e-16</v>
@@ -2785,11 +2785,11 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
         <v>3.203426503814917e-16</v>
@@ -2804,10 +2804,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G41" t="n">
-        <v>4.290677160902923</v>
+        <v>3.797347748702223</v>
       </c>
       <c r="H41" t="n">
-        <v>5.454739923312576</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I41" t="n">
         <v>3.203426503814917e-16</v>
@@ -2825,32 +2825,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N41" t="n">
-        <v>3.635588573791124</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O41" t="n">
-        <v>4.739539537830033</v>
+        <v>6.434359193595686</v>
       </c>
       <c r="P41" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.38565369249775</v>
       </c>
       <c r="R41" t="n">
-        <v>1.280107919192735</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.330645311988472</v>
       </c>
       <c r="D42" t="n">
         <v>3.203426503814917e-16</v>
@@ -2862,13 +2862,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.872231802852783</v>
       </c>
       <c r="H42" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I42" t="n">
-        <v>6.08037341646402</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J42" t="n">
         <v>3.203426503814917e-16</v>
@@ -2883,16 +2883,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.87148525947732</v>
       </c>
       <c r="O42" t="n">
-        <v>5.101538026462062</v>
+        <v>4.741875508290013</v>
       </c>
       <c r="P42" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.330645311988472</v>
       </c>
       <c r="R42" t="n">
         <v>3.203426503814917e-16</v>
@@ -2901,17 +2901,17 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>DR-157</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.34845438939755</v>
       </c>
       <c r="D43" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5997595026492368</v>
       </c>
       <c r="E43" t="n">
         <v>3.203426503814917e-16</v>
@@ -2920,13 +2920,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G43" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.038523071803344</v>
       </c>
       <c r="H43" t="n">
-        <v>5.462819553754064</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I43" t="n">
-        <v>1.445799753049531</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J43" t="n">
         <v>3.203426503814917e-16</v>
@@ -2938,486 +2938,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M43" t="n">
-        <v>1.445799753049531</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N43" t="n">
-        <v>2.625834782136685</v>
+        <v>3.126305317145071</v>
       </c>
       <c r="O43" t="n">
-        <v>5.149046271766396</v>
+        <v>6.203209230748278</v>
       </c>
       <c r="P43" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.625834782136685</v>
+        <v>3.126305317145071</v>
       </c>
       <c r="R43" t="n">
-        <v>3.266140316701616</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>S65</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="D44" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E44" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F44" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3.797347748702223</v>
-      </c>
-      <c r="H44" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I44" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J44" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K44" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L44" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M44" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N44" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="O44" t="n">
-        <v>6.434359193595686</v>
-      </c>
-      <c r="P44" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1.38565369249775</v>
-      </c>
-      <c r="R44" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>S69</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>3</v>
-      </c>
-      <c r="C45" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="D45" t="n">
-        <v>3.946466801649578</v>
-      </c>
-      <c r="E45" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F45" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G45" t="n">
-        <v>4.742376604145422</v>
-      </c>
-      <c r="H45" t="n">
-        <v>1.341269817188368</v>
-      </c>
-      <c r="I45" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.6901908350612248</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1.911015109459704</v>
-      </c>
-      <c r="L45" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M45" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N45" t="n">
-        <v>3.350844299056191</v>
-      </c>
-      <c r="O45" t="n">
-        <v>5.416765153834561</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.654086861375977</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.6901908350612248</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.155097583764673</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>S70</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.4821516951373809</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2.622632918687211</v>
-      </c>
-      <c r="E46" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F46" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G46" t="n">
-        <v>5.780526748697312</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1.757429696725922</v>
-      </c>
-      <c r="I46" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1.757429696725922</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.8428990389152713</v>
-      </c>
-      <c r="L46" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N46" t="n">
-        <v>3.775936825679039</v>
-      </c>
-      <c r="O46" t="n">
-        <v>4.435289923305293</v>
-      </c>
-      <c r="P46" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0.4821516951373809</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.131244533278253</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>S72</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.5574817642990493</v>
-      </c>
-      <c r="D47" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E47" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F47" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G47" t="n">
-        <v>3.623018726983231</v>
-      </c>
-      <c r="H47" t="n">
-        <v>5.487612545182457</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.3055025469742512</v>
-      </c>
-      <c r="J47" t="n">
-        <v>1.272079545436801</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L47" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N47" t="n">
-        <v>4.008481476755091</v>
-      </c>
-      <c r="O47" t="n">
-        <v>4.789256798126342</v>
-      </c>
-      <c r="P47" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0.9585800726200192</v>
-      </c>
-      <c r="R47" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>S74</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>3</v>
-      </c>
-      <c r="C48" t="n">
-        <v>2.813555626621104</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1.812524024831787</v>
-      </c>
-      <c r="E48" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F48" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G48" t="n">
-        <v>5.062297041796164</v>
-      </c>
-      <c r="H48" t="n">
-        <v>3.328438136200979</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.5873770536544561</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2.465351050405582</v>
-      </c>
-      <c r="K48" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L48" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N48" t="n">
-        <v>4.072890040163067</v>
-      </c>
-      <c r="O48" t="n">
-        <v>4.801387467107483</v>
-      </c>
-      <c r="P48" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1.70545004745549</v>
-      </c>
-      <c r="R48" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="D49" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E49" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F49" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G49" t="n">
-        <v>5.884219765410462</v>
-      </c>
-      <c r="H49" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I49" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J49" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K49" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L49" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M49" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3.797347748702223</v>
-      </c>
-      <c r="O49" t="n">
-        <v>4.908441047171919</v>
-      </c>
-      <c r="P49" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="R49" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="n">
-        <v>1.349358265727701</v>
-      </c>
-      <c r="D50" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E50" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F50" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G50" t="n">
-        <v>4.616440732194325</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.3891234984260248</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.6952767815530165</v>
-      </c>
-      <c r="J50" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K50" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L50" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.3891234984260248</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1.514796482951849</v>
-      </c>
-      <c r="O50" t="n">
-        <v>6.167876379727164</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0.9476979983300771</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="R50" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="n">
-        <v>1.330645311988472</v>
-      </c>
-      <c r="D51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G51" t="n">
-        <v>5.872231802852783</v>
-      </c>
-      <c r="H51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N51" t="n">
-        <v>3.87148525947732</v>
-      </c>
-      <c r="O51" t="n">
-        <v>4.741875508290013</v>
-      </c>
-      <c r="P51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1.330645311988472</v>
-      </c>
-      <c r="R51" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.838879010391133</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/reference_taxa_clusters.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/reference_taxa_clusters.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,32 +581,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>DR-10</t>
+          <t>DR-94</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>2.010888316142736</v>
+        <v>0.6884318358631885</v>
       </c>
       <c r="D3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.248813912524715</v>
       </c>
       <c r="E3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7373619340108534</v>
       </c>
       <c r="F3" t="n">
-        <v>2.010888316142736</v>
+        <v>1.939625328694575</v>
       </c>
       <c r="G3" t="n">
-        <v>5.714661819801716</v>
+        <v>2.700142468802172</v>
       </c>
       <c r="H3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.07318654233476171</v>
       </c>
       <c r="I3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.914290962876675</v>
       </c>
       <c r="J3" t="n">
         <v>3.203426503814917e-16</v>
@@ -618,38 +618,38 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.1541276431784817</v>
       </c>
       <c r="N3" t="n">
-        <v>4.968230419506606</v>
+        <v>2.702066573517365</v>
       </c>
       <c r="O3" t="n">
-        <v>3.713829095368272</v>
+        <v>6.150618145712828</v>
       </c>
       <c r="P3" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.489033763922271</v>
       </c>
       <c r="R3" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7373619340108534</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>DR-54</t>
+          <t>DR-103</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D4" t="n">
-        <v>3.025535092107138</v>
+        <v>5.554329793490393</v>
       </c>
       <c r="E4" t="n">
         <v>3.203426503814917e-16</v>
@@ -658,13 +658,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G4" t="n">
-        <v>4.093511885923145</v>
+        <v>2.697158200792512</v>
       </c>
       <c r="H4" t="n">
-        <v>4.59778654107874</v>
+        <v>4.321014707683134</v>
       </c>
       <c r="I4" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.820340563652085</v>
       </c>
       <c r="J4" t="n">
         <v>3.203426503814917e-16</v>
@@ -676,13 +676,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M4" t="n">
-        <v>3.311586150665903</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N4" t="n">
-        <v>3.025535092107138</v>
+        <v>2.697158200792512</v>
       </c>
       <c r="O4" t="n">
-        <v>5.266786540694901</v>
+        <v>3.172627943761552</v>
       </c>
       <c r="P4" t="n">
         <v>3.203426503814917e-16</v>
@@ -691,17 +691,17 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R4" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.858190887474038</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DR-163</t>
+          <t>SCR-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>3.203426503814917e-16</v>
@@ -716,10 +716,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G5" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.077683437568725</v>
       </c>
       <c r="H5" t="n">
-        <v>6.398031073973154</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I5" t="n">
         <v>3.203426503814917e-16</v>
@@ -737,10 +737,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N5" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.727234056148433</v>
       </c>
       <c r="O5" t="n">
-        <v>4.142957953842043</v>
+        <v>6.57694211380182</v>
       </c>
       <c r="P5" t="n">
         <v>3.203426503814917e-16</v>
@@ -755,17 +755,17 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DR-164</t>
+          <t>SCR-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D6" t="n">
-        <v>4.045233364735362</v>
+        <v>0.7862933065297747</v>
       </c>
       <c r="E6" t="n">
         <v>3.203426503814917e-16</v>
@@ -774,10 +774,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G6" t="n">
-        <v>1.264986512097531</v>
+        <v>4.142957953842043</v>
       </c>
       <c r="H6" t="n">
-        <v>6.309004397742273</v>
+        <v>4.362134417282382</v>
       </c>
       <c r="I6" t="n">
         <v>3.203426503814917e-16</v>
@@ -789,19 +789,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L6" t="n">
-        <v>1.68511366861321</v>
+        <v>4.362134417282382</v>
       </c>
       <c r="M6" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8579075100879084</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O6" t="n">
-        <v>1.471200911255877</v>
+        <v>2.602281976921183</v>
       </c>
       <c r="P6" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.300335979246591</v>
       </c>
       <c r="Q6" t="n">
         <v>3.203426503814917e-16</v>
@@ -813,7 +813,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>DR-167</t>
+          <t>LSC-07</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -823,7 +823,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5556469338966</v>
+        <v>1.960720012338189</v>
       </c>
       <c r="E7" t="n">
         <v>3.203426503814917e-16</v>
@@ -832,37 +832,37 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G7" t="n">
-        <v>5.635374126367335</v>
+        <v>5.648855220576159</v>
       </c>
       <c r="H7" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.464301023360515</v>
       </c>
       <c r="I7" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.616412139346209</v>
       </c>
       <c r="J7" t="n">
-        <v>2.76955288934522</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7194478329081769</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L7" t="n">
-        <v>1.197301440373618</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8969065070358966</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5170584362193528</v>
+        <v>3.448551513972233</v>
       </c>
       <c r="O7" t="n">
-        <v>5.368130103004817</v>
+        <v>3.87148525947732</v>
       </c>
       <c r="P7" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.4989892776113035</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8690393221168372</v>
       </c>
       <c r="R7" t="n">
         <v>3.203426503814917e-16</v>
@@ -871,32 +871,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>DR-168</t>
+          <t>DR-125</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D8" t="n">
-        <v>5.881934108295542</v>
+        <v>1.521268267965566</v>
       </c>
       <c r="E8" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.06931984661941622</v>
       </c>
       <c r="F8" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G8" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5737941364358816</v>
       </c>
       <c r="H8" t="n">
-        <v>5.273559133363798</v>
+        <v>4.194039469520115</v>
       </c>
       <c r="I8" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.115153634365784</v>
       </c>
       <c r="J8" t="n">
         <v>3.203426503814917e-16</v>
@@ -905,56 +905,56 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L8" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9609381470343171</v>
       </c>
       <c r="M8" t="n">
-        <v>1.292354979504015</v>
+        <v>6.217107805232111</v>
       </c>
       <c r="N8" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="O8" t="n">
-        <v>1.962937905778455</v>
+        <v>2.412498628442507</v>
       </c>
       <c r="P8" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.09511887896221638</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.1649942856112457</v>
       </c>
       <c r="R8" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3434958112538121</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>DR-175</t>
+          <t>LSC-09</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7015976723254892</v>
       </c>
       <c r="D9" t="n">
-        <v>1.745427172914403</v>
+        <v>3.318611206510286</v>
       </c>
       <c r="E9" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.775158340656881</v>
       </c>
       <c r="F9" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G9" t="n">
-        <v>4.126856279550426</v>
+        <v>5.172850259602431</v>
       </c>
       <c r="H9" t="n">
-        <v>2.179323699444562</v>
+        <v>1.720913610124057</v>
       </c>
       <c r="I9" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.801534553146519</v>
       </c>
       <c r="J9" t="n">
         <v>3.203426503814917e-16</v>
@@ -966,74 +966,74 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M9" t="n">
-        <v>1.121990524378611</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N9" t="n">
-        <v>1.121990524378611</v>
+        <v>1.80950466920085</v>
       </c>
       <c r="O9" t="n">
-        <v>6.25349992300136</v>
+        <v>4.976371289815223</v>
       </c>
       <c r="P9" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7015976723254892</v>
       </c>
       <c r="Q9" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R9" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7015976723254892</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>DR-195</t>
+          <t>LSC-12</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1.150242635580613</v>
+        <v>1.330645311988472</v>
       </c>
       <c r="D10" t="n">
-        <v>1.150242635580613</v>
+        <v>3.713829095368272</v>
       </c>
       <c r="E10" t="n">
-        <v>3.721932779208732</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="F10" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G10" t="n">
-        <v>6.304671300699757</v>
+        <v>5.036423408249874</v>
       </c>
       <c r="H10" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I10" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.100264123473429</v>
       </c>
       <c r="J10" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.896653486982127</v>
       </c>
       <c r="K10" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L10" t="n">
-        <v>1.150242635580613</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M10" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N10" t="n">
-        <v>2.827323338290201</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="O10" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.334984247712809</v>
       </c>
       <c r="P10" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.010888316142736</v>
       </c>
       <c r="Q10" t="n">
         <v>3.203426503814917e-16</v>
@@ -1045,7 +1045,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DR-197</t>
+          <t>SCR-04</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1064,7 +1064,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G11" t="n">
-        <v>6.051070184214275</v>
+        <v>5.672425341971495</v>
       </c>
       <c r="H11" t="n">
         <v>3.203426503814917e-16</v>
@@ -1085,10 +1085,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N11" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.584962500721157</v>
       </c>
       <c r="O11" t="n">
-        <v>5.157604729806445</v>
+        <v>5.523561956057013</v>
       </c>
       <c r="P11" t="n">
         <v>3.203426503814917e-16</v>
@@ -1103,14 +1103,14 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DR-202</t>
+          <t>SCR-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.350716518311987</v>
       </c>
       <c r="D12" t="n">
         <v>3.203426503814917e-16</v>
@@ -1122,7 +1122,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G12" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.350259665639975</v>
       </c>
       <c r="H12" t="n">
         <v>3.203426503814917e-16</v>
@@ -1140,50 +1140,50 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M12" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.331588205937932</v>
       </c>
       <c r="N12" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.196600538156653</v>
       </c>
       <c r="O12" t="n">
-        <v>6.658211482751795</v>
+        <v>5.78825675019676</v>
       </c>
       <c r="P12" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.024030069363076</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.331588205937932</v>
       </c>
       <c r="R12" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.350716518311987</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-204</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.68332477441813</v>
       </c>
       <c r="E13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.373282005376731</v>
       </c>
       <c r="F13" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.921229298351621</v>
       </c>
       <c r="H13" t="n">
-        <v>5.357552004618084</v>
+        <v>6.178487014945737</v>
       </c>
       <c r="I13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1195,16 +1195,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.048197292966219</v>
       </c>
       <c r="M13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.259259362142412</v>
       </c>
       <c r="N13" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="O13" t="n">
-        <v>5.930737337562887</v>
+        <v>2.164889411545014</v>
       </c>
       <c r="P13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1213,23 +1213,23 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.455312898831799</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-205</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7649411668273915</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D14" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7691161177699127</v>
       </c>
       <c r="E14" t="n">
         <v>3.203426503814917e-16</v>
@@ -1238,13 +1238,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2324460860003711</v>
+        <v>1.268105395381216</v>
       </c>
       <c r="H14" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2324460860003711</v>
+        <v>0.7691161177699127</v>
       </c>
       <c r="J14" t="n">
         <v>3.203426503814917e-16</v>
@@ -1253,16 +1253,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2324460860003711</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M14" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.914995645245574</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7649411668273915</v>
+        <v>6.369643421843278</v>
       </c>
       <c r="O14" t="n">
-        <v>6.630477159973525</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P14" t="n">
         <v>3.203426503814917e-16</v>
@@ -1271,20 +1271,20 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R14" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.268105395381216</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>DR-206</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>2.605196984461211</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D15" t="n">
         <v>3.203426503814917e-16</v>
@@ -1296,7 +1296,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G15" t="n">
-        <v>3.244061423481349</v>
+        <v>4.876972617710485</v>
       </c>
       <c r="H15" t="n">
         <v>3.203426503814917e-16</v>
@@ -1317,71 +1317,71 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N15" t="n">
-        <v>5.64825093183208</v>
+        <v>2.02033099828571</v>
       </c>
       <c r="O15" t="n">
-        <v>5.258825506031243</v>
+        <v>6.101935543140568</v>
       </c>
       <c r="P15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7268502500741482</v>
       </c>
       <c r="Q15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.284917523732244</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>DR-207</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D16" t="n">
-        <v>1.200819009388096</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5618788876081152</v>
       </c>
       <c r="F16" t="n">
-        <v>1.200819009388096</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G16" t="n">
-        <v>2.291634172573763</v>
+        <v>5.985977433133131</v>
       </c>
       <c r="H16" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.947532580105865</v>
       </c>
       <c r="J16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.538419914784126</v>
       </c>
       <c r="K16" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.947532580105865</v>
       </c>
       <c r="M16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.115477217419936</v>
       </c>
       <c r="N16" t="n">
-        <v>3.334984247712808</v>
+        <v>3.328781765928425</v>
       </c>
       <c r="O16" t="n">
-        <v>6.416427414239525</v>
+        <v>4.142957953842043</v>
       </c>
       <c r="P16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5618788876081152</v>
       </c>
       <c r="Q16" t="n">
         <v>3.203426503814917e-16</v>
@@ -1393,17 +1393,17 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>DR-208</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.907772708164823</v>
       </c>
       <c r="D17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.223337521298769</v>
       </c>
       <c r="E17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1412,13 +1412,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G17" t="n">
-        <v>1.343954401217361</v>
+        <v>3.346859325384784</v>
       </c>
       <c r="H17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.786884066556411</v>
       </c>
       <c r="I17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.471414204472197</v>
       </c>
       <c r="J17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1427,22 +1427,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.404868132997189</v>
       </c>
       <c r="M17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.482114093129406</v>
       </c>
       <c r="N17" t="n">
-        <v>2.027480736422107</v>
+        <v>1.503278703127448</v>
       </c>
       <c r="O17" t="n">
-        <v>6.590730981180768</v>
+        <v>4.204077523956366</v>
       </c>
       <c r="P17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.503278703127448</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.503278703127448</v>
       </c>
       <c r="R17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1451,17 +1451,17 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>DR-209</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.908283830908385</v>
       </c>
       <c r="D18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.1952562913989341</v>
       </c>
       <c r="E18" t="n">
         <v>3.203426503814917e-16</v>
@@ -1470,92 +1470,92 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.392815161283227</v>
       </c>
       <c r="H18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.52810016376548</v>
       </c>
       <c r="I18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5208321633014408</v>
       </c>
       <c r="J18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9027027986450852</v>
       </c>
       <c r="K18" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L18" t="n">
-        <v>1.902932582039835</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3672089741882289</v>
       </c>
       <c r="N18" t="n">
-        <v>1.244803668756707</v>
+        <v>1.375291320486087</v>
       </c>
       <c r="O18" t="n">
-        <v>6.598281987085227</v>
+        <v>5.626608427361777</v>
       </c>
       <c r="P18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.110644063683993</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.204358498506187</v>
       </c>
       <c r="R18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.1952562913989341</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>DR-15</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7907111659377324</v>
+        <v>1.025928464990526</v>
       </c>
       <c r="D19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.744049522542173</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7907111659377324</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G19" t="n">
-        <v>4.372118352313833</v>
+        <v>3.294001658435625</v>
       </c>
       <c r="H19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.632147644270419</v>
       </c>
       <c r="I19" t="n">
-        <v>1.970746195024886</v>
+        <v>1.844254504869133</v>
       </c>
       <c r="J19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7907111659377324</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.259487160731418</v>
       </c>
       <c r="M19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.749895472819714</v>
       </c>
       <c r="N19" t="n">
-        <v>4.881035788519983</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O19" t="n">
-        <v>5.576380898876536</v>
+        <v>2.210059327853142</v>
       </c>
       <c r="P19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.210059327853142</v>
       </c>
       <c r="Q19" t="n">
         <v>3.203426503814917e-16</v>
@@ -1567,26 +1567,26 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>DR-17</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5686078878708545</v>
       </c>
       <c r="D20" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.975398026766922</v>
       </c>
       <c r="F20" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.444464777216034</v>
       </c>
       <c r="H20" t="n">
         <v>3.203426503814917e-16</v>
@@ -1595,25 +1595,25 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.975398026766922</v>
       </c>
       <c r="K20" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.28236101050746</v>
       </c>
       <c r="M20" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.953521680942322</v>
       </c>
       <c r="O20" t="n">
-        <v>6.658211482751795</v>
+        <v>5.427236921208487</v>
       </c>
       <c r="P20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.123096750288245</v>
       </c>
       <c r="Q20" t="n">
         <v>3.203426503814917e-16</v>
@@ -1625,56 +1625,56 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>DR-18</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6716424538336574</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D21" t="n">
-        <v>1.128142095540397</v>
+        <v>0.9928402084271342</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6716424538336574</v>
+        <v>0.5801932565732844</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6716424538336574</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G21" t="n">
-        <v>6.148943747704833</v>
+        <v>4.07395594291159</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8403736653519254</v>
+        <v>2.158772140503586</v>
       </c>
       <c r="I21" t="n">
-        <v>0.260180408778641</v>
+        <v>3.235090048108769</v>
       </c>
       <c r="J21" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4805307985768705</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4805307985768705</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.797115737552766</v>
       </c>
       <c r="N21" t="n">
-        <v>1.666262602823005</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O21" t="n">
-        <v>4.592309300379081</v>
+        <v>5.963153611563069</v>
       </c>
       <c r="P21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5801932565732844</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.894457614762477</v>
       </c>
       <c r="R21" t="n">
         <v>3.203426503814917e-16</v>
@@ -1683,56 +1683,56 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>DR-19</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.256339753259786</v>
       </c>
       <c r="D22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.565913046718168</v>
       </c>
       <c r="F22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.317915032380738</v>
       </c>
       <c r="H22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.256339753259786</v>
       </c>
       <c r="I22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.358854663885719</v>
       </c>
       <c r="J22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5488932460136344</v>
       </c>
       <c r="K22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5488932460136344</v>
       </c>
       <c r="L22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5488932460136344</v>
       </c>
       <c r="M22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N22" t="n">
-        <v>0.795180208111502</v>
+        <v>1.917537839808027</v>
       </c>
       <c r="O22" t="n">
-        <v>6.647670042889607</v>
+        <v>4.448460500816294</v>
       </c>
       <c r="P22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.256339753259786</v>
       </c>
       <c r="R22" t="n">
         <v>3.203426503814917e-16</v>
@@ -1741,26 +1741,26 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>DR-20</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3263154121283017</v>
       </c>
       <c r="D23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E23" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.08875461424297566</v>
       </c>
       <c r="F23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G23" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.998740754099797</v>
       </c>
       <c r="H23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1778,19 +1778,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M23" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6517437797578886</v>
       </c>
       <c r="N23" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.473345203336181</v>
       </c>
       <c r="O23" t="n">
-        <v>6.658211482751795</v>
+        <v>5.142716125671646</v>
       </c>
       <c r="P23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.08875461424297566</v>
       </c>
       <c r="R23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1799,56 +1799,56 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>DR-23</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>1.813821517558835</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9585800726200192</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="F24" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G24" t="n">
-        <v>2.926715573964768</v>
+        <v>5.144054104230877</v>
       </c>
       <c r="H24" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="J24" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3944761767965276</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.85065345479636</v>
       </c>
       <c r="M24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.127523751722153</v>
       </c>
       <c r="N24" t="n">
-        <v>2.255073120131111</v>
+        <v>1.410757771901608</v>
       </c>
       <c r="O24" t="n">
-        <v>6.440438272660687</v>
+        <v>5.889810299081591</v>
       </c>
       <c r="P24" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="R24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1857,32 +1857,32 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>DR-38</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.399421886369236</v>
+        <v>0.4287006624855133</v>
       </c>
       <c r="D25" t="n">
-        <v>4.441858732844736</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E25" t="n">
-        <v>0.399421886369236</v>
+        <v>2.365202356081421</v>
       </c>
       <c r="F25" t="n">
-        <v>0.399421886369236</v>
+        <v>2.040607317244977</v>
       </c>
       <c r="G25" t="n">
-        <v>4.592516646115072</v>
+        <v>5.894272313010426</v>
       </c>
       <c r="H25" t="n">
-        <v>4.3657782510295</v>
+        <v>1.44895580751278</v>
       </c>
       <c r="I25" t="n">
-        <v>1.186447986673725</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J25" t="n">
         <v>3.203426503814917e-16</v>
@@ -1891,16 +1891,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9685979008608663</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M25" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>3.28864350317529</v>
+        <v>3.370521499177415</v>
       </c>
       <c r="O25" t="n">
-        <v>4.648634242809477</v>
+        <v>4.575153180193171</v>
       </c>
       <c r="P25" t="n">
         <v>3.203426503814917e-16</v>
@@ -1909,32 +1909,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5641038958234921</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>DR-40</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>2.438263439136034</v>
+        <v>0.4989892776113035</v>
       </c>
       <c r="D26" t="n">
-        <v>1.911665100928866</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8690393221168372</v>
       </c>
       <c r="F26" t="n">
-        <v>1.073801300410117</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G26" t="n">
-        <v>4.223388413810172</v>
+        <v>5.38919132179204</v>
       </c>
       <c r="H26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1949,16 +1949,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6345804331377208</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M26" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N26" t="n">
-        <v>4.629759124069301</v>
+        <v>1.163285804079277</v>
       </c>
       <c r="O26" t="n">
-        <v>5.648789573465464</v>
+        <v>5.848286675010258</v>
       </c>
       <c r="P26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1967,23 +1967,23 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R26" t="n">
-        <v>0.6345804331377208</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>DR-44</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.888578717331577</v>
       </c>
       <c r="E27" t="n">
         <v>3.203426503814917e-16</v>
@@ -1992,13 +1992,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G27" t="n">
-        <v>2.010888316142736</v>
+        <v>4.662451872030237</v>
       </c>
       <c r="H27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7447429447579256</v>
       </c>
       <c r="I27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.597901556428655</v>
       </c>
       <c r="J27" t="n">
         <v>3.203426503814917e-16</v>
@@ -2013,53 +2013,53 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N27" t="n">
-        <v>5.101538026462062</v>
+        <v>1.888578717331577</v>
       </c>
       <c r="O27" t="n">
-        <v>6.014274130982118</v>
+        <v>6.056161680855508</v>
       </c>
       <c r="P27" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.233490130219779</v>
       </c>
       <c r="R27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7447429447579256</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>DR-45</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8654578766211725</v>
       </c>
       <c r="D28" t="n">
-        <v>2.345292087952873</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E28" t="n">
-        <v>3.195861790625938</v>
+        <v>1.067563283812635</v>
       </c>
       <c r="F28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.902932582039835</v>
       </c>
       <c r="G28" t="n">
-        <v>3.934112064343543</v>
+        <v>4.254154983721236</v>
       </c>
       <c r="H28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.183584401348678</v>
       </c>
       <c r="I28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.022063735665987</v>
       </c>
       <c r="J28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.695871814459378</v>
       </c>
       <c r="K28" t="n">
         <v>3.203426503814917e-16</v>
@@ -2071,29 +2071,29 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N28" t="n">
-        <v>2.345292087952873</v>
+        <v>2.273699814391163</v>
       </c>
       <c r="O28" t="n">
-        <v>6.137252569345645</v>
+        <v>4.42947839653567</v>
       </c>
       <c r="P28" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.273699814391163</v>
       </c>
       <c r="R28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.067563283812635</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>DR-48</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>3.203426503814917e-16</v>
@@ -2102,13 +2102,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4378774756369554</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G29" t="n">
-        <v>1.045323990509491</v>
+        <v>6.131155431277737</v>
       </c>
       <c r="H29" t="n">
         <v>3.203426503814917e-16</v>
@@ -2129,10 +2129,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N29" t="n">
-        <v>3.745382295550968</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O29" t="n">
-        <v>6.445763325802663</v>
+        <v>4.995895601667264</v>
       </c>
       <c r="P29" t="n">
         <v>3.203426503814917e-16</v>
@@ -2147,32 +2147,32 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>DR-49</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1.357552004618084</v>
+        <v>1.304854581528421</v>
       </c>
       <c r="D30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E30" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.584962500721157</v>
       </c>
       <c r="F30" t="n">
-        <v>1.357552004618084</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G30" t="n">
-        <v>2.857980995127572</v>
+        <v>6.082462160191973</v>
       </c>
       <c r="H30" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6674246609131292</v>
       </c>
       <c r="I30" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3719687773869582</v>
       </c>
       <c r="J30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2187,16 +2187,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N30" t="n">
-        <v>5.988684686772165</v>
+        <v>1.745427172914402</v>
       </c>
       <c r="O30" t="n">
-        <v>4.864186144654281</v>
+        <v>4.527247002864868</v>
       </c>
       <c r="P30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.304854581528421</v>
       </c>
       <c r="R30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2205,32 +2205,32 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>DR-50</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D31" t="n">
-        <v>1.769618811484958</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.508772937544713</v>
       </c>
       <c r="F31" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.871125674841771</v>
       </c>
       <c r="H31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3183614798671702</v>
       </c>
       <c r="I31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7997013495141689</v>
       </c>
       <c r="J31" t="n">
         <v>3.203426503814917e-16</v>
@@ -2242,19 +2242,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7997013495141689</v>
       </c>
       <c r="N31" t="n">
-        <v>5.584600333017261</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O31" t="n">
-        <v>5.689366530544118</v>
+        <v>5.172396639944554</v>
       </c>
       <c r="P31" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9910668752299923</v>
       </c>
       <c r="R31" t="n">
         <v>3.203426503814917e-16</v>
@@ -2263,11 +2263,11 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>DR-51</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
         <v>3.203426503814917e-16</v>
@@ -2279,19 +2279,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="F32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="G32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.853451336647058</v>
       </c>
       <c r="H32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="I32" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.212993723334198</v>
       </c>
       <c r="K32" t="n">
         <v>3.203426503814917e-16</v>
@@ -2303,50 +2303,50 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N32" t="n">
-        <v>2.646890249864358</v>
+        <v>2.740240726199067</v>
       </c>
       <c r="O32" t="n">
-        <v>6.5810023142079</v>
+        <v>5.056268219646745</v>
       </c>
       <c r="P32" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="R32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.2954558835261716</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>DR-53</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.321928094887362</v>
       </c>
       <c r="D33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.321928094887362</v>
       </c>
       <c r="E33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.222392421336448</v>
       </c>
       <c r="F33" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.309855262586788</v>
       </c>
       <c r="H33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.874469117916141</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7447429447579256</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J33" t="n">
         <v>3.203426503814917e-16</v>
@@ -2358,19 +2358,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.874469117916141</v>
       </c>
       <c r="N33" t="n">
-        <v>3.075948853233299</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O33" t="n">
-        <v>6.537480770743348</v>
+        <v>4.92283213947754</v>
       </c>
       <c r="P33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.087462841250339</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.222392421336448</v>
       </c>
       <c r="R33" t="n">
         <v>3.203426503814917e-16</v>
@@ -2379,50 +2379,50 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>DR-55</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.121073858184611</v>
       </c>
       <c r="D34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.337776487737098</v>
       </c>
       <c r="E34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.040948046747595</v>
       </c>
       <c r="F34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G34" t="n">
-        <v>2.206161150578032</v>
+        <v>5.983670193378476</v>
       </c>
       <c r="H34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.121073858184611</v>
       </c>
       <c r="J34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.555850752479857</v>
       </c>
       <c r="K34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.1602862091746009</v>
       </c>
       <c r="M34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N34" t="n">
-        <v>3.566008174993656</v>
+        <v>1.526139447180877</v>
       </c>
       <c r="O34" t="n">
-        <v>6.435331368836803</v>
+        <v>4.958019323407682</v>
       </c>
       <c r="P34" t="n">
         <v>3.203426503814917e-16</v>
@@ -2431,13 +2431,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3045316322762159</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>DR-56</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2447,7 +2447,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D35" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.547487795302493</v>
       </c>
       <c r="E35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2456,7 +2456,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G35" t="n">
-        <v>2.584962500721157</v>
+        <v>4.989558253278354</v>
       </c>
       <c r="H35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2471,38 +2471,38 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L35" t="n">
-        <v>2.584962500721157</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M35" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N35" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.119739244274096</v>
       </c>
       <c r="O35" t="n">
-        <v>6.507794640198696</v>
+        <v>5.725825036561006</v>
       </c>
       <c r="P35" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.758991900496205</v>
       </c>
       <c r="R35" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.547487795302493</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>DR-59</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.82797653267369</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2514,7 +2514,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G36" t="n">
-        <v>1.350716518311988</v>
+        <v>4.452050332173762</v>
       </c>
       <c r="H36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2523,7 +2523,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J36" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.1770226328017681</v>
       </c>
       <c r="K36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2535,16 +2535,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N36" t="n">
-        <v>2.285688951456035</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O36" t="n">
-        <v>6.56679155955111</v>
+        <v>6.312148355328148</v>
       </c>
       <c r="P36" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6061514912755392</v>
       </c>
       <c r="R36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2553,32 +2553,32 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-09</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7015976723254892</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D37" t="n">
-        <v>3.318611206510286</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E37" t="n">
-        <v>2.775158340656881</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F37" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G37" t="n">
-        <v>5.172850259602431</v>
+        <v>6.086383652788929</v>
       </c>
       <c r="H37" t="n">
-        <v>1.720913610124057</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I37" t="n">
-        <v>3.801534553146519</v>
+        <v>2.501061243112211</v>
       </c>
       <c r="J37" t="n">
         <v>3.203426503814917e-16</v>
@@ -2593,32 +2593,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N37" t="n">
-        <v>1.80950466920085</v>
+        <v>2.267104070142841</v>
       </c>
       <c r="O37" t="n">
-        <v>4.976371289815223</v>
+        <v>4.52568669140555</v>
       </c>
       <c r="P37" t="n">
-        <v>0.7015976723254892</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.430239905922514</v>
       </c>
       <c r="R37" t="n">
-        <v>0.7015976723254892</v>
+        <v>0.8855412754150851</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>DR-140</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="D38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2630,7 +2630,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G38" t="n">
-        <v>3.225220681487266</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="H38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2651,16 +2651,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N38" t="n">
-        <v>4.82031925463496</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="O38" t="n">
-        <v>6.021391865052195</v>
+        <v>4.53743413063857</v>
       </c>
       <c r="P38" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.525628361338754</v>
+        <v>5.506032031499436</v>
       </c>
       <c r="R38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2669,32 +2669,32 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G39" t="n">
-        <v>5.144054104230877</v>
+        <v>4.290677160902923</v>
       </c>
       <c r="H39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.454739923312576</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J39" t="n">
         <v>3.203426503814917e-16</v>
@@ -2703,31 +2703,31 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L39" t="n">
-        <v>1.85065345479636</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M39" t="n">
-        <v>1.127523751722153</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N39" t="n">
-        <v>1.410757771901608</v>
+        <v>3.635588573791124</v>
       </c>
       <c r="O39" t="n">
-        <v>5.889810299081591</v>
+        <v>4.739539537830033</v>
       </c>
       <c r="P39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.280107919192735</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2746,13 +2746,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G40" t="n">
-        <v>6.131155431277737</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H40" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I40" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.08037341646402</v>
       </c>
       <c r="J40" t="n">
         <v>3.203426503814917e-16</v>
@@ -2770,7 +2770,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="O40" t="n">
-        <v>4.995895601667264</v>
+        <v>5.101538026462062</v>
       </c>
       <c r="P40" t="n">
         <v>3.203426503814917e-16</v>
@@ -2785,11 +2785,11 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
         <v>3.203426503814917e-16</v>
@@ -2804,13 +2804,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G41" t="n">
-        <v>3.797347748702223</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H41" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.462819553754064</v>
       </c>
       <c r="I41" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.445799753049531</v>
       </c>
       <c r="J41" t="n">
         <v>3.203426503814917e-16</v>
@@ -2822,77 +2822,77 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M41" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.445799753049531</v>
       </c>
       <c r="N41" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.625834782136685</v>
       </c>
       <c r="O41" t="n">
-        <v>6.434359193595686</v>
+        <v>5.149046271766396</v>
       </c>
       <c r="P41" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.38565369249775</v>
+        <v>2.625834782136685</v>
       </c>
       <c r="R41" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.266140316701616</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>1.330645311988472</v>
+        <v>0.2497922947652635</v>
       </c>
       <c r="D42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.708598241528256</v>
       </c>
       <c r="E42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.2497922947652635</v>
       </c>
       <c r="F42" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G42" t="n">
-        <v>5.872231802852783</v>
+        <v>3.6255224140106</v>
       </c>
       <c r="H42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.230308796476028</v>
       </c>
       <c r="I42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8124108742686269</v>
       </c>
       <c r="J42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.2497922947652635</v>
       </c>
       <c r="K42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.778232429365308</v>
       </c>
       <c r="L42" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.711307528786242</v>
       </c>
       <c r="N42" t="n">
-        <v>3.87148525947732</v>
+        <v>4.273253579717254</v>
       </c>
       <c r="O42" t="n">
-        <v>4.741875508290013</v>
+        <v>4.708285303808026</v>
       </c>
       <c r="P42" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.330645311988472</v>
+        <v>2.778232429365308</v>
       </c>
       <c r="R42" t="n">
         <v>3.203426503814917e-16</v>
@@ -2901,59 +2901,1045 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
+          <t>LSC-45</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4.15677962538539</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.5947435215137417</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.192645077942396</v>
+      </c>
+      <c r="O43" t="n">
+        <v>6.29555811169563</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.339486466271667</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>LSC-47</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.366007313171981</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3.659279427970584</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.6360019337216219</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N44" t="n">
+        <v>4.462878920255767</v>
+      </c>
+      <c r="O44" t="n">
+        <v>5.991042828457422</v>
+      </c>
+      <c r="P44" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="R44" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>LSC-48</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3.147876741128932</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4.424571275087995</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.1995849749625519</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.6721734968035544</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1.396185513119206</v>
+      </c>
+      <c r="L45" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N45" t="n">
+        <v>5.311940290169167</v>
+      </c>
+      <c r="O45" t="n">
+        <v>4.87471233571952</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.027561507636242</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.1995849749625519</v>
+      </c>
+      <c r="R45" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>LSC-53</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.797347748702223</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I46" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="O46" t="n">
+        <v>6.434359193595686</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.38565369249775</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>LSC-55</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.5825679855807736</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.5825679855807736</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4.122499655249576</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4.037635732043608</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.9964067352759918</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1.580169489532257</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N47" t="n">
+        <v>2.45354706238544</v>
+      </c>
+      <c r="O47" t="n">
+        <v>5.774295360253894</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.31761510201628</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.31761510201628</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.994606741229781</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>LSC-56</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G48" t="n">
+        <v>4.612163162004862</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2.411694056204474</v>
+      </c>
+      <c r="L48" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.6935729986528256</v>
+      </c>
+      <c r="O48" t="n">
+        <v>6.132079184757066</v>
+      </c>
+      <c r="P48" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.794576317336301</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>LSC-57</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3.946466801649578</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.742376604145422</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.341269817188368</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.6901908350612248</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1.911015109459704</v>
+      </c>
+      <c r="L49" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3.350844299056191</v>
+      </c>
+      <c r="O49" t="n">
+        <v>5.416765153834561</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.654086861375977</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.6901908350612248</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.155097583764673</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>LSC-58</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.4821516951373809</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.622632918687211</v>
+      </c>
+      <c r="E50" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F50" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5.780526748697312</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.757429696725922</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.757429696725922</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.8428990389152713</v>
+      </c>
+      <c r="L50" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3.775936825679039</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4.435289923305293</v>
+      </c>
+      <c r="P50" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.4821516951373809</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.131244533278253</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>LSC-59</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.5574817642990493</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3.623018726983231</v>
+      </c>
+      <c r="H51" t="n">
+        <v>5.487612545182457</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.3055025469742512</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.272079545436801</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4.008481476755091</v>
+      </c>
+      <c r="O51" t="n">
+        <v>4.789256798126342</v>
+      </c>
+      <c r="P51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.9585800726200192</v>
+      </c>
+      <c r="R51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>LSC-60</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2.813555626621104</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.812524024831787</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F52" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5.062297041796164</v>
+      </c>
+      <c r="H52" t="n">
+        <v>3.328438136200979</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.5873770536544561</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.465351050405582</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L52" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4.072890040163067</v>
+      </c>
+      <c r="O52" t="n">
+        <v>4.801387467107483</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.70545004745549</v>
+      </c>
+      <c r="R52" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5.884219765410462</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3.797347748702223</v>
+      </c>
+      <c r="O53" t="n">
+        <v>4.908441047171919</v>
+      </c>
+      <c r="P53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="R53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1.349358265727701</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4.616440732194325</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.3891234984260248</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.6952767815530165</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.3891234984260248</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1.514796482951849</v>
+      </c>
+      <c r="O54" t="n">
+        <v>6.167876379727164</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.9476979983300771</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="R54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1.330645311988472</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5.872231802852783</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3.87148525947732</v>
+      </c>
+      <c r="O55" t="n">
+        <v>4.741875508290013</v>
+      </c>
+      <c r="P55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.330645311988472</v>
+      </c>
+      <c r="R55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.9585800726200192</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G56" t="n">
+        <v>4.312369266462518</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2.515253528909752</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N56" t="n">
+        <v>4.090661722917659</v>
+      </c>
+      <c r="O56" t="n">
+        <v>5.917287628211485</v>
+      </c>
+      <c r="P56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="R56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5.3375904957025</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2.385528257116121</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="O57" t="n">
+        <v>5.768743472787629</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.268105395381216</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.268105395381216</v>
+      </c>
+      <c r="R57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5.317915032380739</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.598259323334614</v>
+      </c>
+      <c r="O58" t="n">
+        <v>5.672425341971495</v>
+      </c>
+      <c r="P58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="R58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
           <t>DR-157</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="n">
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
         <v>1.34845438939755</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D59" t="n">
         <v>0.5997595026492368</v>
       </c>
-      <c r="E43" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F43" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="E59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G59" t="n">
         <v>3.038523071803344</v>
       </c>
-      <c r="H43" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I43" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J43" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K43" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L43" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N43" t="n">
+      <c r="H59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N59" t="n">
         <v>3.126305317145071</v>
       </c>
-      <c r="O43" t="n">
+      <c r="O59" t="n">
         <v>6.203209230748278</v>
       </c>
-      <c r="P43" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q43" t="n">
+      <c r="P59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q59" t="n">
         <v>3.126305317145071</v>
       </c>
-      <c r="R43" t="n">
+      <c r="R59" t="n">
         <v>1.838879010391133</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>DR-159</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2.493040011280117</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2.233797184608697</v>
+      </c>
+      <c r="O60" t="n">
+        <v>6.533978572002351</v>
+      </c>
+      <c r="P60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="R60" t="n">
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/reference_taxa_clusters.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/reference_taxa_clusters.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>3.203426503814917e-16</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>3.203426503814917e-16</v>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>1.330645311988472</v>
@@ -1161,32 +1161,32 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-141</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D13" t="n">
-        <v>3.68332477441813</v>
+        <v>0.7691161177699127</v>
       </c>
       <c r="E13" t="n">
-        <v>2.373282005376731</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F13" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G13" t="n">
-        <v>1.921229298351621</v>
+        <v>1.268105395381216</v>
       </c>
       <c r="H13" t="n">
-        <v>6.178487014945737</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7691161177699127</v>
       </c>
       <c r="J13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1195,16 +1195,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L13" t="n">
-        <v>2.048197292966219</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M13" t="n">
-        <v>1.259259362142412</v>
+        <v>3.914995645245574</v>
       </c>
       <c r="N13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.369643421843278</v>
       </c>
       <c r="O13" t="n">
-        <v>2.164889411545014</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1213,23 +1213,23 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R13" t="n">
-        <v>1.455312898831799</v>
+        <v>1.268105395381216</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7691161177699127</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E14" t="n">
         <v>3.203426503814917e-16</v>
@@ -1238,13 +1238,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G14" t="n">
-        <v>1.268105395381216</v>
+        <v>4.876972617710485</v>
       </c>
       <c r="H14" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7691161177699127</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J14" t="n">
         <v>3.203426503814917e-16</v>
@@ -1256,28 +1256,28 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M14" t="n">
-        <v>3.914995645245574</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N14" t="n">
-        <v>6.369643421843278</v>
+        <v>2.02033099828571</v>
       </c>
       <c r="O14" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.101935543140568</v>
       </c>
       <c r="P14" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7268502500741482</v>
       </c>
       <c r="Q14" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R14" t="n">
-        <v>1.268105395381216</v>
+        <v>0.284917523732244</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1290,101 +1290,101 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5618788876081152</v>
       </c>
       <c r="F15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G15" t="n">
-        <v>4.876972617710485</v>
+        <v>5.985977433133131</v>
       </c>
       <c r="H15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.947532580105865</v>
       </c>
       <c r="J15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.538419914784126</v>
       </c>
       <c r="K15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.947532580105865</v>
       </c>
       <c r="M15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.115477217419936</v>
       </c>
       <c r="N15" t="n">
-        <v>2.02033099828571</v>
+        <v>3.328781765928425</v>
       </c>
       <c r="O15" t="n">
-        <v>6.101935543140568</v>
+        <v>4.142957953842043</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7268502500741482</v>
+        <v>0.5618788876081152</v>
       </c>
       <c r="Q15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R15" t="n">
-        <v>0.284917523732244</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.907772708164823</v>
       </c>
       <c r="D16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.223337521298769</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5618788876081152</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F16" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G16" t="n">
-        <v>5.985977433133131</v>
+        <v>3.346859325384784</v>
       </c>
       <c r="H16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.786884066556411</v>
       </c>
       <c r="I16" t="n">
-        <v>1.947532580105865</v>
+        <v>3.471414204472197</v>
       </c>
       <c r="J16" t="n">
-        <v>1.538419914784126</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K16" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L16" t="n">
-        <v>1.947532580105865</v>
+        <v>4.404868132997189</v>
       </c>
       <c r="M16" t="n">
-        <v>2.115477217419936</v>
+        <v>2.482114093129406</v>
       </c>
       <c r="N16" t="n">
-        <v>3.328781765928425</v>
+        <v>1.503278703127448</v>
       </c>
       <c r="O16" t="n">
-        <v>4.142957953842043</v>
+        <v>4.204077523956366</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5618788876081152</v>
+        <v>1.503278703127448</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.503278703127448</v>
       </c>
       <c r="R16" t="n">
         <v>3.203426503814917e-16</v>
@@ -1393,17 +1393,17 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1.907772708164823</v>
+        <v>1.908283830908385</v>
       </c>
       <c r="D17" t="n">
-        <v>2.223337521298769</v>
+        <v>0.1952562913989341</v>
       </c>
       <c r="E17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1412,56 +1412,56 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G17" t="n">
-        <v>3.346859325384784</v>
+        <v>5.392815161283227</v>
       </c>
       <c r="H17" t="n">
-        <v>4.786884066556411</v>
+        <v>1.52810016376548</v>
       </c>
       <c r="I17" t="n">
-        <v>3.471414204472197</v>
+        <v>0.5208321633014408</v>
       </c>
       <c r="J17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9027027986450852</v>
       </c>
       <c r="K17" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L17" t="n">
-        <v>4.404868132997189</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M17" t="n">
-        <v>2.482114093129406</v>
+        <v>0.3672089741882289</v>
       </c>
       <c r="N17" t="n">
-        <v>1.503278703127448</v>
+        <v>1.375291320486087</v>
       </c>
       <c r="O17" t="n">
-        <v>4.204077523956366</v>
+        <v>5.626608427361777</v>
       </c>
       <c r="P17" t="n">
-        <v>1.503278703127448</v>
+        <v>1.110644063683993</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.503278703127448</v>
+        <v>1.204358498506187</v>
       </c>
       <c r="R17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.1952562913989341</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>1.908283830908385</v>
+        <v>1.025928464990526</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1952562913989341</v>
+        <v>2.744049522542173</v>
       </c>
       <c r="E18" t="n">
         <v>3.203426503814917e-16</v>
@@ -1470,92 +1470,92 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G18" t="n">
-        <v>5.392815161283227</v>
+        <v>3.294001658435625</v>
       </c>
       <c r="H18" t="n">
-        <v>1.52810016376548</v>
+        <v>3.632147644270419</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5208321633014408</v>
+        <v>1.844254504869133</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9027027986450852</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K18" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.259487160731418</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3672089741882289</v>
+        <v>4.749895472819714</v>
       </c>
       <c r="N18" t="n">
-        <v>1.375291320486087</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O18" t="n">
-        <v>5.626608427361777</v>
+        <v>2.210059327853142</v>
       </c>
       <c r="P18" t="n">
-        <v>1.110644063683993</v>
+        <v>2.210059327853142</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.204358498506187</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1952562913989341</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1.025928464990526</v>
+        <v>0.5686078878708545</v>
       </c>
       <c r="D19" t="n">
-        <v>2.744049522542173</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.975398026766922</v>
       </c>
       <c r="F19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G19" t="n">
-        <v>3.294001658435625</v>
+        <v>4.444464777216034</v>
       </c>
       <c r="H19" t="n">
-        <v>3.632147644270419</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I19" t="n">
-        <v>1.844254504869133</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.975398026766922</v>
       </c>
       <c r="K19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L19" t="n">
-        <v>5.259487160731418</v>
+        <v>2.28236101050746</v>
       </c>
       <c r="M19" t="n">
-        <v>4.749895472819714</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.953521680942322</v>
       </c>
       <c r="O19" t="n">
-        <v>2.210059327853142</v>
+        <v>5.427236921208487</v>
       </c>
       <c r="P19" t="n">
-        <v>2.210059327853142</v>
+        <v>4.123096750288245</v>
       </c>
       <c r="Q19" t="n">
         <v>3.203426503814917e-16</v>
@@ -1567,56 +1567,56 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5686078878708545</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9928402084271342</v>
       </c>
       <c r="E20" t="n">
-        <v>0.975398026766922</v>
+        <v>0.5801932565732844</v>
       </c>
       <c r="F20" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G20" t="n">
-        <v>4.444464777216034</v>
+        <v>4.07395594291159</v>
       </c>
       <c r="H20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.158772140503586</v>
       </c>
       <c r="I20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.235090048108769</v>
       </c>
       <c r="J20" t="n">
-        <v>0.975398026766922</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K20" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L20" t="n">
-        <v>2.28236101050746</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.797115737552766</v>
       </c>
       <c r="N20" t="n">
-        <v>3.953521680942322</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O20" t="n">
-        <v>5.427236921208487</v>
+        <v>5.963153611563069</v>
       </c>
       <c r="P20" t="n">
-        <v>4.123096750288245</v>
+        <v>0.5801932565732844</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.894457614762477</v>
       </c>
       <c r="R20" t="n">
         <v>3.203426503814917e-16</v>
@@ -1625,56 +1625,56 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.256339753259786</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9928402084271342</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5801932565732844</v>
+        <v>4.565913046718168</v>
       </c>
       <c r="F21" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G21" t="n">
-        <v>4.07395594291159</v>
+        <v>5.317915032380738</v>
       </c>
       <c r="H21" t="n">
-        <v>2.158772140503586</v>
+        <v>1.256339753259786</v>
       </c>
       <c r="I21" t="n">
-        <v>3.235090048108769</v>
+        <v>3.358854663885719</v>
       </c>
       <c r="J21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5488932460136344</v>
       </c>
       <c r="K21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5488932460136344</v>
       </c>
       <c r="L21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5488932460136344</v>
       </c>
       <c r="M21" t="n">
-        <v>1.797115737552766</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.917537839808027</v>
       </c>
       <c r="O21" t="n">
-        <v>5.963153611563069</v>
+        <v>4.448460500816294</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5801932565732844</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.894457614762477</v>
+        <v>1.256339753259786</v>
       </c>
       <c r="R21" t="n">
         <v>3.203426503814917e-16</v>
@@ -1683,56 +1683,56 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1.256339753259786</v>
+        <v>0.3263154121283017</v>
       </c>
       <c r="D22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E22" t="n">
-        <v>4.565913046718168</v>
+        <v>0.08875461424297566</v>
       </c>
       <c r="F22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G22" t="n">
-        <v>5.317915032380738</v>
+        <v>5.998740754099797</v>
       </c>
       <c r="H22" t="n">
-        <v>1.256339753259786</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I22" t="n">
-        <v>3.358854663885719</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5488932460136344</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5488932460136344</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5488932460136344</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6517437797578886</v>
       </c>
       <c r="N22" t="n">
-        <v>1.917537839808027</v>
+        <v>1.473345203336181</v>
       </c>
       <c r="O22" t="n">
-        <v>4.448460500816294</v>
+        <v>5.142716125671646</v>
       </c>
       <c r="P22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.256339753259786</v>
+        <v>0.08875461424297566</v>
       </c>
       <c r="R22" t="n">
         <v>3.203426503814917e-16</v>
@@ -1741,32 +1741,32 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3263154121283017</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="D23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08875461424297566</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="F23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G23" t="n">
-        <v>5.998740754099797</v>
+        <v>5.144054104230877</v>
       </c>
       <c r="H23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I23" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="J23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1775,22 +1775,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L23" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.85065345479636</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6517437797578886</v>
+        <v>1.127523751722153</v>
       </c>
       <c r="N23" t="n">
-        <v>1.473345203336181</v>
+        <v>1.410757771901608</v>
       </c>
       <c r="O23" t="n">
-        <v>5.142716125671646</v>
+        <v>5.889810299081591</v>
       </c>
       <c r="P23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.08875461424297566</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="R23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1799,32 +1799,32 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5596715814234172</v>
+        <v>0.4287006624855133</v>
       </c>
       <c r="D24" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5596715814234172</v>
+        <v>2.365202356081421</v>
       </c>
       <c r="F24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.040607317244977</v>
       </c>
       <c r="G24" t="n">
-        <v>5.144054104230877</v>
+        <v>5.894272313010426</v>
       </c>
       <c r="H24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.44895580751278</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1833,22 +1833,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L24" t="n">
-        <v>1.85065345479636</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M24" t="n">
-        <v>1.127523751722153</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N24" t="n">
-        <v>1.410757771901608</v>
+        <v>3.370521499177415</v>
       </c>
       <c r="O24" t="n">
-        <v>5.889810299081591</v>
+        <v>4.575153180193171</v>
       </c>
       <c r="P24" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1857,29 +1857,29 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4287006624855133</v>
+        <v>0.4989892776113035</v>
       </c>
       <c r="D25" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E25" t="n">
-        <v>2.365202356081421</v>
+        <v>0.8690393221168372</v>
       </c>
       <c r="F25" t="n">
-        <v>2.040607317244977</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G25" t="n">
-        <v>5.894272313010426</v>
+        <v>5.38919132179204</v>
       </c>
       <c r="H25" t="n">
-        <v>1.44895580751278</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I25" t="n">
         <v>3.203426503814917e-16</v>
@@ -1897,10 +1897,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>3.370521499177415</v>
+        <v>1.163285804079277</v>
       </c>
       <c r="O25" t="n">
-        <v>4.575153180193171</v>
+        <v>5.848286675010258</v>
       </c>
       <c r="P25" t="n">
         <v>3.203426503814917e-16</v>
@@ -1915,32 +1915,32 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4989892776113035</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.888578717331577</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8690393221168372</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F26" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G26" t="n">
-        <v>5.38919132179204</v>
+        <v>4.662451872030237</v>
       </c>
       <c r="H26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7447429447579256</v>
       </c>
       <c r="I26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.597901556428655</v>
       </c>
       <c r="J26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1955,53 +1955,53 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N26" t="n">
-        <v>1.163285804079277</v>
+        <v>1.888578717331577</v>
       </c>
       <c r="O26" t="n">
-        <v>5.848286675010258</v>
+        <v>6.056161680855508</v>
       </c>
       <c r="P26" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.233490130219779</v>
       </c>
       <c r="R26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7447429447579256</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8654578766211725</v>
       </c>
       <c r="D27" t="n">
-        <v>1.888578717331577</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.067563283812635</v>
       </c>
       <c r="F27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.902932582039835</v>
       </c>
       <c r="G27" t="n">
-        <v>4.662451872030237</v>
+        <v>4.254154983721236</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7447429447579256</v>
+        <v>5.183584401348678</v>
       </c>
       <c r="I27" t="n">
-        <v>1.597901556428655</v>
+        <v>3.022063735665987</v>
       </c>
       <c r="J27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.695871814459378</v>
       </c>
       <c r="K27" t="n">
         <v>3.203426503814917e-16</v>
@@ -2013,53 +2013,53 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N27" t="n">
-        <v>1.888578717331577</v>
+        <v>2.273699814391163</v>
       </c>
       <c r="O27" t="n">
-        <v>6.056161680855508</v>
+        <v>4.42947839653567</v>
       </c>
       <c r="P27" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.233490130219779</v>
+        <v>2.273699814391163</v>
       </c>
       <c r="R27" t="n">
-        <v>0.7447429447579256</v>
+        <v>1.067563283812635</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8654578766211725</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D28" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E28" t="n">
-        <v>1.067563283812635</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F28" t="n">
-        <v>1.902932582039835</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G28" t="n">
-        <v>4.254154983721236</v>
+        <v>6.131155431277737</v>
       </c>
       <c r="H28" t="n">
-        <v>5.183584401348678</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I28" t="n">
-        <v>3.022063735665987</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J28" t="n">
-        <v>2.695871814459378</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K28" t="n">
         <v>3.203426503814917e-16</v>
@@ -2071,50 +2071,50 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N28" t="n">
-        <v>2.273699814391163</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O28" t="n">
-        <v>4.42947839653567</v>
+        <v>4.995895601667264</v>
       </c>
       <c r="P28" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.273699814391163</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R28" t="n">
-        <v>1.067563283812635</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.304854581528421</v>
       </c>
       <c r="D29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.584962500721157</v>
       </c>
       <c r="F29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G29" t="n">
-        <v>6.131155431277737</v>
+        <v>6.082462160191973</v>
       </c>
       <c r="H29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6674246609131292</v>
       </c>
       <c r="I29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3719687773869582</v>
       </c>
       <c r="J29" t="n">
         <v>3.203426503814917e-16</v>
@@ -2129,16 +2129,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.745427172914402</v>
       </c>
       <c r="O29" t="n">
-        <v>4.995895601667264</v>
+        <v>4.527247002864868</v>
       </c>
       <c r="P29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.304854581528421</v>
       </c>
       <c r="R29" t="n">
         <v>3.203426503814917e-16</v>
@@ -2147,32 +2147,32 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1.304854581528421</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E30" t="n">
-        <v>2.584962500721157</v>
+        <v>2.508772937544713</v>
       </c>
       <c r="F30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G30" t="n">
-        <v>6.082462160191973</v>
+        <v>5.871125674841771</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6674246609131292</v>
+        <v>0.3183614798671702</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3719687773869582</v>
+        <v>0.7997013495141689</v>
       </c>
       <c r="J30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2184,19 +2184,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M30" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7997013495141689</v>
       </c>
       <c r="N30" t="n">
-        <v>1.745427172914402</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O30" t="n">
-        <v>4.527247002864868</v>
+        <v>5.172396639944554</v>
       </c>
       <c r="P30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.304854581528421</v>
+        <v>0.9910668752299923</v>
       </c>
       <c r="R30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2205,7 +2205,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2218,22 +2218,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E31" t="n">
-        <v>2.508772937544713</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="G31" t="n">
-        <v>5.871125674841771</v>
+        <v>5.853451336647058</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3183614798671702</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7997013495141689</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.212993723334198</v>
       </c>
       <c r="K31" t="n">
         <v>3.203426503814917e-16</v>
@@ -2242,56 +2242,56 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7997013495141689</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.740240726199067</v>
       </c>
       <c r="O31" t="n">
-        <v>5.172396639944554</v>
+        <v>5.056268219646745</v>
       </c>
       <c r="P31" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9910668752299923</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="R31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.2954558835261716</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.321928094887362</v>
       </c>
       <c r="D32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.321928094887362</v>
       </c>
       <c r="E32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.222392421336448</v>
       </c>
       <c r="F32" t="n">
-        <v>0.540568381362703</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G32" t="n">
-        <v>5.853451336647058</v>
+        <v>5.309855262586788</v>
       </c>
       <c r="H32" t="n">
-        <v>0.540568381362703</v>
+        <v>1.874469117916141</v>
       </c>
       <c r="I32" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J32" t="n">
-        <v>2.212993723334198</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K32" t="n">
         <v>3.203426503814917e-16</v>
@@ -2300,56 +2300,56 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.874469117916141</v>
       </c>
       <c r="N32" t="n">
-        <v>2.740240726199067</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O32" t="n">
-        <v>5.056268219646745</v>
+        <v>4.92283213947754</v>
       </c>
       <c r="P32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.087462841250339</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.540568381362703</v>
+        <v>1.222392421336448</v>
       </c>
       <c r="R32" t="n">
-        <v>0.2954558835261716</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>2.321928094887362</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D33" t="n">
-        <v>2.321928094887362</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E33" t="n">
-        <v>1.222392421336448</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F33" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G33" t="n">
-        <v>5.309855262586788</v>
+        <v>4.452050332173762</v>
       </c>
       <c r="H33" t="n">
-        <v>1.874469117916141</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I33" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.1770226328017681</v>
       </c>
       <c r="K33" t="n">
         <v>3.203426503814917e-16</v>
@@ -2358,19 +2358,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M33" t="n">
-        <v>1.874469117916141</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N33" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="O33" t="n">
-        <v>4.92283213947754</v>
+        <v>6.312148355328148</v>
       </c>
       <c r="P33" t="n">
-        <v>4.087462841250339</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.222392421336448</v>
+        <v>0.6061514912755392</v>
       </c>
       <c r="R33" t="n">
         <v>3.203426503814917e-16</v>
@@ -2379,75 +2379,75 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-30</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>1.121073858184611</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D34" t="n">
-        <v>1.337776487737098</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E34" t="n">
-        <v>1.040948046747595</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G34" t="n">
-        <v>5.983670193378476</v>
+        <v>6.086383652788929</v>
       </c>
       <c r="H34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I34" t="n">
-        <v>1.121073858184611</v>
+        <v>2.501061243112211</v>
       </c>
       <c r="J34" t="n">
-        <v>0.555850752479857</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1602862091746009</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N34" t="n">
-        <v>1.526139447180877</v>
+        <v>2.267104070142841</v>
       </c>
       <c r="O34" t="n">
-        <v>4.958019323407682</v>
+        <v>4.52568669140555</v>
       </c>
       <c r="P34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.430239905922514</v>
       </c>
       <c r="R34" t="n">
-        <v>0.3045316322762159</v>
+        <v>0.8855412754150851</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-32</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="D35" t="n">
-        <v>1.547487795302493</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2456,7 +2456,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G35" t="n">
-        <v>4.989558253278354</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="H35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2477,29 +2477,29 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N35" t="n">
-        <v>3.119739244274096</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="O35" t="n">
-        <v>5.725825036561006</v>
+        <v>4.53743413063857</v>
       </c>
       <c r="P35" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.758991900496205</v>
+        <v>5.506032031499436</v>
       </c>
       <c r="R35" t="n">
-        <v>1.547487795302493</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2514,16 +2514,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G36" t="n">
-        <v>4.452050332173762</v>
+        <v>4.290677160902923</v>
       </c>
       <c r="H36" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.454739923312576</v>
       </c>
       <c r="I36" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1770226328017681</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2535,25 +2535,25 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N36" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.635588573791124</v>
       </c>
       <c r="O36" t="n">
-        <v>6.312148355328148</v>
+        <v>4.739539537830033</v>
       </c>
       <c r="P36" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.6061514912755392</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R36" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.280107919192735</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2572,13 +2572,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G37" t="n">
-        <v>6.086383652788929</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H37" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I37" t="n">
-        <v>2.501061243112211</v>
+        <v>6.08037341646402</v>
       </c>
       <c r="J37" t="n">
         <v>3.203426503814917e-16</v>
@@ -2593,32 +2593,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N37" t="n">
-        <v>2.267104070142841</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O37" t="n">
-        <v>4.52568669140555</v>
+        <v>5.101538026462062</v>
       </c>
       <c r="P37" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.430239905922514</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R37" t="n">
-        <v>0.8855412754150851</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>3.598259323334614</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2630,13 +2630,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G38" t="n">
-        <v>3.598259323334614</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H38" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.462819553754064</v>
       </c>
       <c r="I38" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.445799753049531</v>
       </c>
       <c r="J38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2648,86 +2648,86 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M38" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.445799753049531</v>
       </c>
       <c r="N38" t="n">
-        <v>3.598259323334614</v>
+        <v>2.625834782136685</v>
       </c>
       <c r="O38" t="n">
-        <v>4.53743413063857</v>
+        <v>5.149046271766396</v>
       </c>
       <c r="P38" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.506032031499436</v>
+        <v>2.625834782136685</v>
       </c>
       <c r="R38" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.266140316701616</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.2497922947652635</v>
       </c>
       <c r="D39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.708598241528256</v>
       </c>
       <c r="E39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.2497922947652635</v>
       </c>
       <c r="F39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G39" t="n">
-        <v>4.290677160902923</v>
+        <v>3.6255224140106</v>
       </c>
       <c r="H39" t="n">
-        <v>5.454739923312576</v>
+        <v>4.230308796476028</v>
       </c>
       <c r="I39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8124108742686269</v>
       </c>
       <c r="J39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.2497922947652635</v>
       </c>
       <c r="K39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.778232429365308</v>
       </c>
       <c r="L39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.711307528786242</v>
       </c>
       <c r="N39" t="n">
-        <v>3.635588573791124</v>
+        <v>4.273253579717254</v>
       </c>
       <c r="O39" t="n">
-        <v>4.739539537830033</v>
+        <v>4.708285303808026</v>
       </c>
       <c r="P39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.778232429365308</v>
       </c>
       <c r="R39" t="n">
-        <v>1.280107919192735</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2746,16 +2746,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G40" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.15677962538539</v>
       </c>
       <c r="H40" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I40" t="n">
-        <v>6.08037341646402</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J40" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5947435215137417</v>
       </c>
       <c r="K40" t="n">
         <v>3.203426503814917e-16</v>
@@ -2767,10 +2767,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N40" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.192645077942396</v>
       </c>
       <c r="O40" t="n">
-        <v>5.101538026462062</v>
+        <v>6.29555811169563</v>
       </c>
       <c r="P40" t="n">
         <v>3.203426503814917e-16</v>
@@ -2779,17 +2779,17 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R40" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.339486466271667</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
         <v>3.203426503814917e-16</v>
@@ -2804,13 +2804,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G41" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.797347748702223</v>
       </c>
       <c r="H41" t="n">
-        <v>5.462819553754064</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I41" t="n">
-        <v>1.445799753049531</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J41" t="n">
         <v>3.203426503814917e-16</v>
@@ -2822,86 +2822,86 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M41" t="n">
-        <v>1.445799753049531</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N41" t="n">
-        <v>2.625834782136685</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O41" t="n">
-        <v>5.149046271766396</v>
+        <v>6.434359193595686</v>
       </c>
       <c r="P41" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.625834782136685</v>
+        <v>1.38565369249775</v>
       </c>
       <c r="R41" t="n">
-        <v>3.266140316701616</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2497922947652635</v>
+        <v>0.5825679855807736</v>
       </c>
       <c r="D42" t="n">
-        <v>1.708598241528256</v>
+        <v>0.5825679855807736</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2497922947652635</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F42" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G42" t="n">
-        <v>3.6255224140106</v>
+        <v>4.122499655249576</v>
       </c>
       <c r="H42" t="n">
-        <v>4.230308796476028</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8124108742686269</v>
+        <v>4.037635732043608</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2497922947652635</v>
+        <v>0.9964067352759918</v>
       </c>
       <c r="K42" t="n">
-        <v>2.778232429365308</v>
+        <v>1.580169489532257</v>
       </c>
       <c r="L42" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M42" t="n">
-        <v>3.711307528786242</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N42" t="n">
-        <v>4.273253579717254</v>
+        <v>2.45354706238544</v>
       </c>
       <c r="O42" t="n">
-        <v>4.708285303808026</v>
+        <v>5.774295360253894</v>
       </c>
       <c r="P42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.31761510201628</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.778232429365308</v>
+        <v>1.31761510201628</v>
       </c>
       <c r="R42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.994606741229781</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2920,7 +2920,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G43" t="n">
-        <v>4.15677962538539</v>
+        <v>4.612163162004862</v>
       </c>
       <c r="H43" t="n">
         <v>3.203426503814917e-16</v>
@@ -2929,10 +2929,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5947435215137417</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K43" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.411694056204474</v>
       </c>
       <c r="L43" t="n">
         <v>3.203426503814917e-16</v>
@@ -2941,25 +2941,25 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N43" t="n">
-        <v>2.192645077942396</v>
+        <v>0.6935729986528256</v>
       </c>
       <c r="O43" t="n">
-        <v>6.29555811169563</v>
+        <v>6.132079184757066</v>
       </c>
       <c r="P43" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.794576317336301</v>
       </c>
       <c r="R43" t="n">
-        <v>1.339486466271667</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-47</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2969,7 +2969,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D44" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.946466801649578</v>
       </c>
       <c r="E44" t="n">
         <v>3.203426503814917e-16</v>
@@ -2978,19 +2978,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G44" t="n">
-        <v>2.366007313171981</v>
+        <v>4.742376604145422</v>
       </c>
       <c r="H44" t="n">
-        <v>3.659279427970584</v>
+        <v>1.341269817188368</v>
       </c>
       <c r="I44" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J44" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6901908350612248</v>
       </c>
       <c r="K44" t="n">
-        <v>0.6360019337216219</v>
+        <v>1.911015109459704</v>
       </c>
       <c r="L44" t="n">
         <v>3.203426503814917e-16</v>
@@ -2999,35 +2999,35 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N44" t="n">
-        <v>4.462878920255767</v>
+        <v>3.350844299056191</v>
       </c>
       <c r="O44" t="n">
-        <v>5.991042828457422</v>
+        <v>5.416765153834561</v>
       </c>
       <c r="P44" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.654086861375977</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6901908350612248</v>
       </c>
       <c r="R44" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.155097583764673</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-48</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.4821516951373809</v>
       </c>
       <c r="D45" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.622632918687211</v>
       </c>
       <c r="E45" t="n">
         <v>3.203426503814917e-16</v>
@@ -3036,19 +3036,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G45" t="n">
-        <v>3.147876741128932</v>
+        <v>5.780526748697312</v>
       </c>
       <c r="H45" t="n">
-        <v>4.424571275087995</v>
+        <v>1.757429696725922</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1995849749625519</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J45" t="n">
-        <v>0.6721734968035544</v>
+        <v>1.757429696725922</v>
       </c>
       <c r="K45" t="n">
-        <v>1.396185513119206</v>
+        <v>0.8428990389152713</v>
       </c>
       <c r="L45" t="n">
         <v>3.203426503814917e-16</v>
@@ -3057,32 +3057,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N45" t="n">
-        <v>5.311940290169167</v>
+        <v>3.775936825679039</v>
       </c>
       <c r="O45" t="n">
-        <v>4.87471233571952</v>
+        <v>4.435289923305293</v>
       </c>
       <c r="P45" t="n">
-        <v>1.027561507636242</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.1995849749625519</v>
+        <v>0.4821516951373809</v>
       </c>
       <c r="R45" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.131244533278253</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5574817642990493</v>
       </c>
       <c r="D46" t="n">
         <v>3.203426503814917e-16</v>
@@ -3094,16 +3094,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G46" t="n">
-        <v>3.797347748702223</v>
+        <v>3.623018726983231</v>
       </c>
       <c r="H46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.487612545182457</v>
       </c>
       <c r="I46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3055025469742512</v>
       </c>
       <c r="J46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.272079545436801</v>
       </c>
       <c r="K46" t="n">
         <v>3.203426503814917e-16</v>
@@ -3115,16 +3115,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N46" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.008481476755091</v>
       </c>
       <c r="O46" t="n">
-        <v>6.434359193595686</v>
+        <v>4.789256798126342</v>
       </c>
       <c r="P46" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.38565369249775</v>
+        <v>0.9585800726200192</v>
       </c>
       <c r="R46" t="n">
         <v>3.203426503814917e-16</v>
@@ -3133,17 +3133,17 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5825679855807736</v>
+        <v>2.813555626621104</v>
       </c>
       <c r="D47" t="n">
-        <v>0.5825679855807736</v>
+        <v>1.812524024831787</v>
       </c>
       <c r="E47" t="n">
         <v>3.203426503814917e-16</v>
@@ -3152,19 +3152,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G47" t="n">
-        <v>4.122499655249576</v>
+        <v>5.062297041796164</v>
       </c>
       <c r="H47" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.328438136200979</v>
       </c>
       <c r="I47" t="n">
-        <v>4.037635732043608</v>
+        <v>0.5873770536544561</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9964067352759918</v>
+        <v>2.465351050405582</v>
       </c>
       <c r="K47" t="n">
-        <v>1.580169489532257</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L47" t="n">
         <v>3.203426503814917e-16</v>
@@ -3173,25 +3173,25 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N47" t="n">
-        <v>2.45354706238544</v>
+        <v>4.072890040163067</v>
       </c>
       <c r="O47" t="n">
-        <v>5.774295360253894</v>
+        <v>4.801387467107483</v>
       </c>
       <c r="P47" t="n">
-        <v>1.31761510201628</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.31761510201628</v>
+        <v>1.70545004745549</v>
       </c>
       <c r="R47" t="n">
-        <v>1.994606741229781</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-62</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -3210,7 +3210,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G48" t="n">
-        <v>4.612163162004862</v>
+        <v>5.884219765410462</v>
       </c>
       <c r="H48" t="n">
         <v>3.203426503814917e-16</v>
@@ -3222,7 +3222,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K48" t="n">
-        <v>2.411694056204474</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L48" t="n">
         <v>3.203426503814917e-16</v>
@@ -3231,16 +3231,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N48" t="n">
-        <v>0.6935729986528256</v>
+        <v>3.797347748702223</v>
       </c>
       <c r="O48" t="n">
-        <v>6.132079184757066</v>
+        <v>4.908441047171919</v>
       </c>
       <c r="P48" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.794576317336301</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R48" t="n">
         <v>3.203426503814917e-16</v>
@@ -3249,17 +3249,17 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>SCR-08</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.349358265727701</v>
       </c>
       <c r="D49" t="n">
-        <v>3.946466801649578</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E49" t="n">
         <v>3.203426503814917e-16</v>
@@ -3268,56 +3268,56 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G49" t="n">
-        <v>4.742376604145422</v>
+        <v>4.616440732194325</v>
       </c>
       <c r="H49" t="n">
-        <v>1.341269817188368</v>
+        <v>0.3891234984260248</v>
       </c>
       <c r="I49" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6952767815530165</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6901908350612248</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K49" t="n">
-        <v>1.911015109459704</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L49" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M49" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.3891234984260248</v>
       </c>
       <c r="N49" t="n">
-        <v>3.350844299056191</v>
+        <v>1.514796482951849</v>
       </c>
       <c r="O49" t="n">
-        <v>5.416765153834561</v>
+        <v>6.167876379727164</v>
       </c>
       <c r="P49" t="n">
-        <v>1.654086861375977</v>
+        <v>0.9476979983300771</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.6901908350612248</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R49" t="n">
-        <v>1.155097583764673</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>DR-144</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4821516951373809</v>
+        <v>1.330645311988472</v>
       </c>
       <c r="D50" t="n">
-        <v>2.622632918687211</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E50" t="n">
         <v>3.203426503814917e-16</v>
@@ -3326,19 +3326,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G50" t="n">
-        <v>5.780526748697312</v>
+        <v>5.872231802852783</v>
       </c>
       <c r="H50" t="n">
-        <v>1.757429696725922</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I50" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J50" t="n">
-        <v>1.757429696725922</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8428990389152713</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L50" t="n">
         <v>3.203426503814917e-16</v>
@@ -3347,32 +3347,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N50" t="n">
-        <v>3.775936825679039</v>
+        <v>3.87148525947732</v>
       </c>
       <c r="O50" t="n">
-        <v>4.435289923305293</v>
+        <v>4.741875508290013</v>
       </c>
       <c r="P50" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.4821516951373809</v>
+        <v>1.330645311988472</v>
       </c>
       <c r="R50" t="n">
-        <v>1.131244533278253</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>DR-145</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5574817642990493</v>
+        <v>0.9585800726200192</v>
       </c>
       <c r="D51" t="n">
         <v>3.203426503814917e-16</v>
@@ -3384,37 +3384,37 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G51" t="n">
-        <v>3.623018726983231</v>
+        <v>4.312369266462518</v>
       </c>
       <c r="H51" t="n">
-        <v>5.487612545182457</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3055025469742512</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J51" t="n">
-        <v>1.272079545436801</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K51" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L51" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.515253528909752</v>
       </c>
       <c r="M51" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N51" t="n">
-        <v>4.008481476755091</v>
+        <v>4.090661722917659</v>
       </c>
       <c r="O51" t="n">
-        <v>4.789256798126342</v>
+        <v>5.917287628211485</v>
       </c>
       <c r="P51" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.9585800726200192</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R51" t="n">
         <v>3.203426503814917e-16</v>
@@ -3423,17 +3423,17 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>SCR-09</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>2.813555626621104</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D52" t="n">
-        <v>1.812524024831787</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E52" t="n">
         <v>3.203426503814917e-16</v>
@@ -3442,37 +3442,37 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G52" t="n">
-        <v>5.062297041796164</v>
+        <v>5.3375904957025</v>
       </c>
       <c r="H52" t="n">
-        <v>3.328438136200979</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5873770536544561</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J52" t="n">
-        <v>2.465351050405582</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K52" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L52" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.385528257116121</v>
       </c>
       <c r="M52" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N52" t="n">
-        <v>4.072890040163067</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O52" t="n">
-        <v>4.801387467107483</v>
+        <v>5.768743472787629</v>
       </c>
       <c r="P52" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.268105395381216</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.70545004745549</v>
+        <v>1.268105395381216</v>
       </c>
       <c r="R52" t="n">
         <v>3.203426503814917e-16</v>
@@ -3481,7 +3481,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>DR-159</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -3500,7 +3500,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G53" t="n">
-        <v>5.884219765410462</v>
+        <v>2.493040011280117</v>
       </c>
       <c r="H53" t="n">
         <v>3.203426503814917e-16</v>
@@ -3521,10 +3521,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N53" t="n">
-        <v>3.797347748702223</v>
+        <v>2.233797184608697</v>
       </c>
       <c r="O53" t="n">
-        <v>4.908441047171919</v>
+        <v>6.533978572002351</v>
       </c>
       <c r="P53" t="n">
         <v>3.203426503814917e-16</v>
@@ -3533,412 +3533,6 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R53" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>SCR-08</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="n">
-        <v>1.349358265727701</v>
-      </c>
-      <c r="D54" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E54" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F54" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G54" t="n">
-        <v>4.616440732194325</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.3891234984260248</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.6952767815530165</v>
-      </c>
-      <c r="J54" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K54" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L54" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.3891234984260248</v>
-      </c>
-      <c r="N54" t="n">
-        <v>1.514796482951849</v>
-      </c>
-      <c r="O54" t="n">
-        <v>6.167876379727164</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0.9476979983300771</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="R54" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>DR-144</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="n">
-        <v>1.330645311988472</v>
-      </c>
-      <c r="D55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G55" t="n">
-        <v>5.872231802852783</v>
-      </c>
-      <c r="H55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N55" t="n">
-        <v>3.87148525947732</v>
-      </c>
-      <c r="O55" t="n">
-        <v>4.741875508290013</v>
-      </c>
-      <c r="P55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1.330645311988472</v>
-      </c>
-      <c r="R55" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>DR-145</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.9585800726200192</v>
-      </c>
-      <c r="D56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G56" t="n">
-        <v>4.312369266462518</v>
-      </c>
-      <c r="H56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2.515253528909752</v>
-      </c>
-      <c r="M56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N56" t="n">
-        <v>4.090661722917659</v>
-      </c>
-      <c r="O56" t="n">
-        <v>5.917287628211485</v>
-      </c>
-      <c r="P56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="R56" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>SCR-09</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="D57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G57" t="n">
-        <v>5.3375904957025</v>
-      </c>
-      <c r="H57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L57" t="n">
-        <v>2.385528257116121</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="O57" t="n">
-        <v>5.768743472787629</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1.268105395381216</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>1.268105395381216</v>
-      </c>
-      <c r="R57" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>DR-156</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="D58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G58" t="n">
-        <v>5.317915032380739</v>
-      </c>
-      <c r="H58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N58" t="n">
-        <v>3.598259323334614</v>
-      </c>
-      <c r="O58" t="n">
-        <v>5.672425341971495</v>
-      </c>
-      <c r="P58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="R58" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>DR-157</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="n">
-        <v>1.34845438939755</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.5997595026492368</v>
-      </c>
-      <c r="E59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G59" t="n">
-        <v>3.038523071803344</v>
-      </c>
-      <c r="H59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N59" t="n">
-        <v>3.126305317145071</v>
-      </c>
-      <c r="O59" t="n">
-        <v>6.203209230748278</v>
-      </c>
-      <c r="P59" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>3.126305317145071</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.838879010391133</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>DR-159</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="D60" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E60" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F60" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G60" t="n">
-        <v>2.493040011280117</v>
-      </c>
-      <c r="H60" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I60" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K60" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L60" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N60" t="n">
-        <v>2.233797184608697</v>
-      </c>
-      <c r="O60" t="n">
-        <v>6.533978572002351</v>
-      </c>
-      <c r="P60" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="R60" t="n">
         <v>3.203426503814917e-16</v>
       </c>
     </row>

--- a/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/reference_taxa_clusters.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/taxa_confidence/reference_taxa_clusters.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>3.203426503814917e-16</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>3.203426503814917e-16</v>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>1.330645311988472</v>
@@ -1161,32 +1161,32 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>DR-143</t>
+          <t>DR-141</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7691161177699127</v>
+        <v>3.68332477441813</v>
       </c>
       <c r="E13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.373282005376731</v>
       </c>
       <c r="F13" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G13" t="n">
-        <v>1.268105395381216</v>
+        <v>1.921229298351621</v>
       </c>
       <c r="H13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.178487014945737</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7691161177699127</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1195,16 +1195,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.048197292966219</v>
       </c>
       <c r="M13" t="n">
-        <v>3.914995645245574</v>
+        <v>1.259259362142412</v>
       </c>
       <c r="N13" t="n">
-        <v>6.369643421843278</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.164889411545014</v>
       </c>
       <c r="P13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1213,23 +1213,23 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R13" t="n">
-        <v>1.268105395381216</v>
+        <v>1.455312898831799</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SCR-11</t>
+          <t>DR-143</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D14" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7691161177699127</v>
       </c>
       <c r="E14" t="n">
         <v>3.203426503814917e-16</v>
@@ -1238,13 +1238,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G14" t="n">
-        <v>4.876972617710485</v>
+        <v>1.268105395381216</v>
       </c>
       <c r="H14" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I14" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7691161177699127</v>
       </c>
       <c r="J14" t="n">
         <v>3.203426503814917e-16</v>
@@ -1256,28 +1256,28 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M14" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.914995645245574</v>
       </c>
       <c r="N14" t="n">
-        <v>2.02033099828571</v>
+        <v>6.369643421843278</v>
       </c>
       <c r="O14" t="n">
-        <v>6.101935543140568</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7268502500741482</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q14" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R14" t="n">
-        <v>0.284917523732244</v>
+        <v>1.268105395381216</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SCR-14</t>
+          <t>SCR-11</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1290,101 +1290,101 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5618788876081152</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G15" t="n">
-        <v>5.985977433133131</v>
+        <v>4.876972617710485</v>
       </c>
       <c r="H15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I15" t="n">
-        <v>1.947532580105865</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J15" t="n">
-        <v>1.538419914784126</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L15" t="n">
-        <v>1.947532580105865</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M15" t="n">
-        <v>2.115477217419936</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N15" t="n">
-        <v>3.328781765928425</v>
+        <v>2.02033099828571</v>
       </c>
       <c r="O15" t="n">
-        <v>4.142957953842043</v>
+        <v>6.101935543140568</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5618788876081152</v>
+        <v>0.7268502500741482</v>
       </c>
       <c r="Q15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.284917523732244</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SCR-17</t>
+          <t>SCR-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1.907772708164823</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D16" t="n">
-        <v>2.223337521298769</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5618788876081152</v>
       </c>
       <c r="F16" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G16" t="n">
-        <v>3.346859325384784</v>
+        <v>5.985977433133131</v>
       </c>
       <c r="H16" t="n">
-        <v>4.786884066556411</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I16" t="n">
-        <v>3.471414204472197</v>
+        <v>1.947532580105865</v>
       </c>
       <c r="J16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.538419914784126</v>
       </c>
       <c r="K16" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L16" t="n">
-        <v>4.404868132997189</v>
+        <v>1.947532580105865</v>
       </c>
       <c r="M16" t="n">
-        <v>2.482114093129406</v>
+        <v>2.115477217419936</v>
       </c>
       <c r="N16" t="n">
-        <v>1.503278703127448</v>
+        <v>3.328781765928425</v>
       </c>
       <c r="O16" t="n">
-        <v>4.204077523956366</v>
+        <v>4.142957953842043</v>
       </c>
       <c r="P16" t="n">
-        <v>1.503278703127448</v>
+        <v>0.5618788876081152</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.503278703127448</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R16" t="n">
         <v>3.203426503814917e-16</v>
@@ -1393,17 +1393,17 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SCR-18</t>
+          <t>SCR-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>1.908283830908385</v>
+        <v>1.907772708164823</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1952562913989341</v>
+        <v>2.223337521298769</v>
       </c>
       <c r="E17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1412,56 +1412,56 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G17" t="n">
-        <v>5.392815161283227</v>
+        <v>3.346859325384784</v>
       </c>
       <c r="H17" t="n">
-        <v>1.52810016376548</v>
+        <v>4.786884066556411</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5208321633014408</v>
+        <v>3.471414204472197</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9027027986450852</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K17" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.404868132997189</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3672089741882289</v>
+        <v>2.482114093129406</v>
       </c>
       <c r="N17" t="n">
-        <v>1.375291320486087</v>
+        <v>1.503278703127448</v>
       </c>
       <c r="O17" t="n">
-        <v>5.626608427361777</v>
+        <v>4.204077523956366</v>
       </c>
       <c r="P17" t="n">
-        <v>1.110644063683993</v>
+        <v>1.503278703127448</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.204358498506187</v>
+        <v>1.503278703127448</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1952562913989341</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SCR-19</t>
+          <t>SCR-18</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1.025928464990526</v>
+        <v>1.908283830908385</v>
       </c>
       <c r="D18" t="n">
-        <v>2.744049522542173</v>
+        <v>0.1952562913989341</v>
       </c>
       <c r="E18" t="n">
         <v>3.203426503814917e-16</v>
@@ -1470,92 +1470,92 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G18" t="n">
-        <v>3.294001658435625</v>
+        <v>5.392815161283227</v>
       </c>
       <c r="H18" t="n">
-        <v>3.632147644270419</v>
+        <v>1.52810016376548</v>
       </c>
       <c r="I18" t="n">
-        <v>1.844254504869133</v>
+        <v>0.5208321633014408</v>
       </c>
       <c r="J18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9027027986450852</v>
       </c>
       <c r="K18" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L18" t="n">
-        <v>5.259487160731418</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M18" t="n">
-        <v>4.749895472819714</v>
+        <v>0.3672089741882289</v>
       </c>
       <c r="N18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.375291320486087</v>
       </c>
       <c r="O18" t="n">
-        <v>2.210059327853142</v>
+        <v>5.626608427361777</v>
       </c>
       <c r="P18" t="n">
-        <v>2.210059327853142</v>
+        <v>1.110644063683993</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.204358498506187</v>
       </c>
       <c r="R18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.1952562913989341</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SCR-20</t>
+          <t>SCR-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5686078878708545</v>
+        <v>1.025928464990526</v>
       </c>
       <c r="D19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.744049522542173</v>
       </c>
       <c r="E19" t="n">
-        <v>0.975398026766922</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G19" t="n">
-        <v>4.444464777216034</v>
+        <v>3.294001658435625</v>
       </c>
       <c r="H19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.632147644270419</v>
       </c>
       <c r="I19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.844254504869133</v>
       </c>
       <c r="J19" t="n">
-        <v>0.975398026766922</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K19" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L19" t="n">
-        <v>2.28236101050746</v>
+        <v>5.259487160731418</v>
       </c>
       <c r="M19" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.749895472819714</v>
       </c>
       <c r="N19" t="n">
-        <v>3.953521680942322</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O19" t="n">
-        <v>5.427236921208487</v>
+        <v>2.210059327853142</v>
       </c>
       <c r="P19" t="n">
-        <v>4.123096750288245</v>
+        <v>2.210059327853142</v>
       </c>
       <c r="Q19" t="n">
         <v>3.203426503814917e-16</v>
@@ -1567,56 +1567,56 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>LSC-14</t>
+          <t>SCR-20</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5686078878708545</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9928402084271342</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5801932565732844</v>
+        <v>0.975398026766922</v>
       </c>
       <c r="F20" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G20" t="n">
-        <v>4.07395594291159</v>
+        <v>4.444464777216034</v>
       </c>
       <c r="H20" t="n">
-        <v>2.158772140503586</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I20" t="n">
-        <v>3.235090048108769</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.975398026766922</v>
       </c>
       <c r="K20" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.28236101050746</v>
       </c>
       <c r="M20" t="n">
-        <v>1.797115737552766</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.953521680942322</v>
       </c>
       <c r="O20" t="n">
-        <v>5.963153611563069</v>
+        <v>5.427236921208487</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5801932565732844</v>
+        <v>4.123096750288245</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.894457614762477</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R20" t="n">
         <v>3.203426503814917e-16</v>
@@ -1625,56 +1625,56 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>LSC-15</t>
+          <t>LSC-14</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1.256339753259786</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9928402084271342</v>
       </c>
       <c r="E21" t="n">
-        <v>4.565913046718168</v>
+        <v>0.5801932565732844</v>
       </c>
       <c r="F21" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G21" t="n">
-        <v>5.317915032380738</v>
+        <v>4.07395594291159</v>
       </c>
       <c r="H21" t="n">
-        <v>1.256339753259786</v>
+        <v>2.158772140503586</v>
       </c>
       <c r="I21" t="n">
-        <v>3.358854663885719</v>
+        <v>3.235090048108769</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5488932460136344</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5488932460136344</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5488932460136344</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.797115737552766</v>
       </c>
       <c r="N21" t="n">
-        <v>1.917537839808027</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O21" t="n">
-        <v>4.448460500816294</v>
+        <v>5.963153611563069</v>
       </c>
       <c r="P21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5801932565732844</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.256339753259786</v>
+        <v>2.894457614762477</v>
       </c>
       <c r="R21" t="n">
         <v>3.203426503814917e-16</v>
@@ -1683,56 +1683,56 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LSC-16</t>
+          <t>LSC-15</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3263154121283017</v>
+        <v>1.256339753259786</v>
       </c>
       <c r="D22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08875461424297566</v>
+        <v>4.565913046718168</v>
       </c>
       <c r="F22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G22" t="n">
-        <v>5.998740754099797</v>
+        <v>5.317915032380738</v>
       </c>
       <c r="H22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.256339753259786</v>
       </c>
       <c r="I22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.358854663885719</v>
       </c>
       <c r="J22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5488932460136344</v>
       </c>
       <c r="K22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5488932460136344</v>
       </c>
       <c r="L22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5488932460136344</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6517437797578886</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N22" t="n">
-        <v>1.473345203336181</v>
+        <v>1.917537839808027</v>
       </c>
       <c r="O22" t="n">
-        <v>5.142716125671646</v>
+        <v>4.448460500816294</v>
       </c>
       <c r="P22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.08875461424297566</v>
+        <v>1.256339753259786</v>
       </c>
       <c r="R22" t="n">
         <v>3.203426503814917e-16</v>
@@ -1741,32 +1741,32 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>LSC-17</t>
+          <t>LSC-16</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5596715814234172</v>
+        <v>0.3263154121283017</v>
       </c>
       <c r="D23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5596715814234172</v>
+        <v>0.08875461424297566</v>
       </c>
       <c r="F23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G23" t="n">
-        <v>5.144054104230877</v>
+        <v>5.998740754099797</v>
       </c>
       <c r="H23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5596715814234172</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1775,22 +1775,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L23" t="n">
-        <v>1.85065345479636</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M23" t="n">
-        <v>1.127523751722153</v>
+        <v>0.6517437797578886</v>
       </c>
       <c r="N23" t="n">
-        <v>1.410757771901608</v>
+        <v>1.473345203336181</v>
       </c>
       <c r="O23" t="n">
-        <v>5.889810299081591</v>
+        <v>5.142716125671646</v>
       </c>
       <c r="P23" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5596715814234172</v>
+        <v>0.08875461424297566</v>
       </c>
       <c r="R23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1799,32 +1799,32 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>LSC-18</t>
+          <t>LSC-17</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4287006624855133</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="D24" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E24" t="n">
-        <v>2.365202356081421</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="F24" t="n">
-        <v>2.040607317244977</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G24" t="n">
-        <v>5.894272313010426</v>
+        <v>5.144054104230877</v>
       </c>
       <c r="H24" t="n">
-        <v>1.44895580751278</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="J24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1833,22 +1833,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.85065345479636</v>
       </c>
       <c r="M24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.127523751722153</v>
       </c>
       <c r="N24" t="n">
-        <v>3.370521499177415</v>
+        <v>1.410757771901608</v>
       </c>
       <c r="O24" t="n">
-        <v>4.575153180193171</v>
+        <v>5.889810299081591</v>
       </c>
       <c r="P24" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5596715814234172</v>
       </c>
       <c r="R24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1857,29 +1857,29 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>LSC-19</t>
+          <t>LSC-18</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4989892776113035</v>
+        <v>0.4287006624855133</v>
       </c>
       <c r="D25" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8690393221168372</v>
+        <v>2.365202356081421</v>
       </c>
       <c r="F25" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.040607317244977</v>
       </c>
       <c r="G25" t="n">
-        <v>5.38919132179204</v>
+        <v>5.894272313010426</v>
       </c>
       <c r="H25" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.44895580751278</v>
       </c>
       <c r="I25" t="n">
         <v>3.203426503814917e-16</v>
@@ -1897,10 +1897,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>1.163285804079277</v>
+        <v>3.370521499177415</v>
       </c>
       <c r="O25" t="n">
-        <v>5.848286675010258</v>
+        <v>4.575153180193171</v>
       </c>
       <c r="P25" t="n">
         <v>3.203426503814917e-16</v>
@@ -1915,32 +1915,32 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>LSC-22</t>
+          <t>LSC-19</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.4989892776113035</v>
       </c>
       <c r="D26" t="n">
-        <v>1.888578717331577</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8690393221168372</v>
       </c>
       <c r="F26" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G26" t="n">
-        <v>4.662451872030237</v>
+        <v>5.38919132179204</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7447429447579256</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I26" t="n">
-        <v>1.597901556428655</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1955,53 +1955,53 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N26" t="n">
-        <v>1.888578717331577</v>
+        <v>1.163285804079277</v>
       </c>
       <c r="O26" t="n">
-        <v>6.056161680855508</v>
+        <v>5.848286675010258</v>
       </c>
       <c r="P26" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.233490130219779</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7447429447579256</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LSC-23</t>
+          <t>LSC-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8654578766211725</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.888578717331577</v>
       </c>
       <c r="E27" t="n">
-        <v>1.067563283812635</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F27" t="n">
-        <v>1.902932582039835</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G27" t="n">
-        <v>4.254154983721236</v>
+        <v>4.662451872030237</v>
       </c>
       <c r="H27" t="n">
-        <v>5.183584401348678</v>
+        <v>0.7447429447579256</v>
       </c>
       <c r="I27" t="n">
-        <v>3.022063735665987</v>
+        <v>1.597901556428655</v>
       </c>
       <c r="J27" t="n">
-        <v>2.695871814459378</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K27" t="n">
         <v>3.203426503814917e-16</v>
@@ -2013,53 +2013,53 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N27" t="n">
-        <v>2.273699814391163</v>
+        <v>1.888578717331577</v>
       </c>
       <c r="O27" t="n">
-        <v>4.42947839653567</v>
+        <v>6.056161680855508</v>
       </c>
       <c r="P27" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.273699814391163</v>
+        <v>1.233490130219779</v>
       </c>
       <c r="R27" t="n">
-        <v>1.067563283812635</v>
+        <v>0.7447429447579256</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>LSC-24</t>
+          <t>LSC-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8654578766211725</v>
       </c>
       <c r="D28" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.067563283812635</v>
       </c>
       <c r="F28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.902932582039835</v>
       </c>
       <c r="G28" t="n">
-        <v>6.131155431277737</v>
+        <v>4.254154983721236</v>
       </c>
       <c r="H28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.183584401348678</v>
       </c>
       <c r="I28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.022063735665987</v>
       </c>
       <c r="J28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.695871814459378</v>
       </c>
       <c r="K28" t="n">
         <v>3.203426503814917e-16</v>
@@ -2071,50 +2071,50 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.273699814391163</v>
       </c>
       <c r="O28" t="n">
-        <v>4.995895601667264</v>
+        <v>4.42947839653567</v>
       </c>
       <c r="P28" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.273699814391163</v>
       </c>
       <c r="R28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.067563283812635</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>LSC-25</t>
+          <t>LSC-24</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1.304854581528421</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E29" t="n">
-        <v>2.584962500721157</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G29" t="n">
-        <v>6.082462160191973</v>
+        <v>6.131155431277737</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6674246609131292</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3719687773869582</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J29" t="n">
         <v>3.203426503814917e-16</v>
@@ -2129,16 +2129,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N29" t="n">
-        <v>1.745427172914402</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O29" t="n">
-        <v>4.527247002864868</v>
+        <v>4.995895601667264</v>
       </c>
       <c r="P29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.304854581528421</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R29" t="n">
         <v>3.203426503814917e-16</v>
@@ -2147,32 +2147,32 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LSC-26</t>
+          <t>LSC-25</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.304854581528421</v>
       </c>
       <c r="D30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E30" t="n">
-        <v>2.508772937544713</v>
+        <v>2.584962500721157</v>
       </c>
       <c r="F30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G30" t="n">
-        <v>5.871125674841771</v>
+        <v>6.082462160191973</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3183614798671702</v>
+        <v>0.6674246609131292</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7997013495141689</v>
+        <v>0.3719687773869582</v>
       </c>
       <c r="J30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2184,19 +2184,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7997013495141689</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N30" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.745427172914402</v>
       </c>
       <c r="O30" t="n">
-        <v>5.172396639944554</v>
+        <v>4.527247002864868</v>
       </c>
       <c r="P30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9910668752299923</v>
+        <v>1.304854581528421</v>
       </c>
       <c r="R30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2205,7 +2205,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>LSC-27</t>
+          <t>LSC-26</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2218,22 +2218,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="E31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.508772937544713</v>
       </c>
       <c r="F31" t="n">
-        <v>0.540568381362703</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G31" t="n">
-        <v>5.853451336647058</v>
+        <v>5.871125674841771</v>
       </c>
       <c r="H31" t="n">
-        <v>0.540568381362703</v>
+        <v>0.3183614798671702</v>
       </c>
       <c r="I31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7997013495141689</v>
       </c>
       <c r="J31" t="n">
-        <v>2.212993723334198</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K31" t="n">
         <v>3.203426503814917e-16</v>
@@ -2242,56 +2242,56 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M31" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7997013495141689</v>
       </c>
       <c r="N31" t="n">
-        <v>2.740240726199067</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O31" t="n">
-        <v>5.056268219646745</v>
+        <v>5.172396639944554</v>
       </c>
       <c r="P31" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.540568381362703</v>
+        <v>0.9910668752299923</v>
       </c>
       <c r="R31" t="n">
-        <v>0.2954558835261716</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SCR-06</t>
+          <t>LSC-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>2.321928094887362</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D32" t="n">
-        <v>2.321928094887362</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E32" t="n">
-        <v>1.222392421336448</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="G32" t="n">
-        <v>5.309855262586788</v>
+        <v>5.853451336647058</v>
       </c>
       <c r="H32" t="n">
-        <v>1.874469117916141</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="I32" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.212993723334198</v>
       </c>
       <c r="K32" t="n">
         <v>3.203426503814917e-16</v>
@@ -2300,56 +2300,56 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M32" t="n">
-        <v>1.874469117916141</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.740240726199067</v>
       </c>
       <c r="O32" t="n">
-        <v>4.92283213947754</v>
+        <v>5.056268219646745</v>
       </c>
       <c r="P32" t="n">
-        <v>4.087462841250339</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.222392421336448</v>
+        <v>0.540568381362703</v>
       </c>
       <c r="R32" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.2954558835261716</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>LSC-37</t>
+          <t>SCR-06</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.321928094887362</v>
       </c>
       <c r="D33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.321928094887362</v>
       </c>
       <c r="E33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.222392421336448</v>
       </c>
       <c r="F33" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G33" t="n">
-        <v>4.452050332173762</v>
+        <v>5.309855262586788</v>
       </c>
       <c r="H33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.874469117916141</v>
       </c>
       <c r="I33" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1770226328017681</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K33" t="n">
         <v>3.203426503814917e-16</v>
@@ -2358,19 +2358,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.874469117916141</v>
       </c>
       <c r="N33" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="O33" t="n">
-        <v>6.312148355328148</v>
+        <v>4.92283213947754</v>
       </c>
       <c r="P33" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.087462841250339</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.6061514912755392</v>
+        <v>1.222392421336448</v>
       </c>
       <c r="R33" t="n">
         <v>3.203426503814917e-16</v>
@@ -2379,75 +2379,75 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>LSC-38</t>
+          <t>LSC-30</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.121073858184611</v>
       </c>
       <c r="D34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.337776487737098</v>
       </c>
       <c r="E34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.040948046747595</v>
       </c>
       <c r="F34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G34" t="n">
-        <v>6.086383652788929</v>
+        <v>5.983670193378476</v>
       </c>
       <c r="H34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I34" t="n">
-        <v>2.501061243112211</v>
+        <v>1.121073858184611</v>
       </c>
       <c r="J34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.555850752479857</v>
       </c>
       <c r="K34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L34" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.1602862091746009</v>
       </c>
       <c r="M34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N34" t="n">
-        <v>2.267104070142841</v>
+        <v>1.526139447180877</v>
       </c>
       <c r="O34" t="n">
-        <v>4.52568669140555</v>
+        <v>4.958019323407682</v>
       </c>
       <c r="P34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.430239905922514</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R34" t="n">
-        <v>0.8855412754150851</v>
+        <v>0.3045316322762159</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>LSC-39</t>
+          <t>LSC-32</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>3.598259323334614</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D35" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.547487795302493</v>
       </c>
       <c r="E35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2456,7 +2456,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G35" t="n">
-        <v>3.598259323334614</v>
+        <v>4.989558253278354</v>
       </c>
       <c r="H35" t="n">
         <v>3.203426503814917e-16</v>
@@ -2477,29 +2477,29 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N35" t="n">
-        <v>3.598259323334614</v>
+        <v>3.119739244274096</v>
       </c>
       <c r="O35" t="n">
-        <v>4.53743413063857</v>
+        <v>5.725825036561006</v>
       </c>
       <c r="P35" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.506032031499436</v>
+        <v>2.758991900496205</v>
       </c>
       <c r="R35" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.547487795302493</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>LSC-40</t>
+          <t>LSC-37</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2514,16 +2514,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G36" t="n">
-        <v>4.290677160902923</v>
+        <v>4.452050332173762</v>
       </c>
       <c r="H36" t="n">
-        <v>5.454739923312576</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I36" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J36" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.1770226328017681</v>
       </c>
       <c r="K36" t="n">
         <v>3.203426503814917e-16</v>
@@ -2535,25 +2535,25 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N36" t="n">
-        <v>3.635588573791124</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O36" t="n">
-        <v>4.739539537830033</v>
+        <v>6.312148355328148</v>
       </c>
       <c r="P36" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6061514912755392</v>
       </c>
       <c r="R36" t="n">
-        <v>1.280107919192735</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>LSC-41</t>
+          <t>LSC-38</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2572,13 +2572,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.086383652788929</v>
       </c>
       <c r="H37" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I37" t="n">
-        <v>6.08037341646402</v>
+        <v>2.501061243112211</v>
       </c>
       <c r="J37" t="n">
         <v>3.203426503814917e-16</v>
@@ -2593,32 +2593,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.267104070142841</v>
       </c>
       <c r="O37" t="n">
-        <v>5.101538026462062</v>
+        <v>4.52568669140555</v>
       </c>
       <c r="P37" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.430239905922514</v>
       </c>
       <c r="R37" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8855412754150851</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>LSC-42</t>
+          <t>LSC-39</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="D38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2630,13 +2630,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G38" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="H38" t="n">
-        <v>5.462819553754064</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I38" t="n">
-        <v>1.445799753049531</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J38" t="n">
         <v>3.203426503814917e-16</v>
@@ -2648,86 +2648,86 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M38" t="n">
-        <v>1.445799753049531</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N38" t="n">
-        <v>2.625834782136685</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="O38" t="n">
-        <v>5.149046271766396</v>
+        <v>4.53743413063857</v>
       </c>
       <c r="P38" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.625834782136685</v>
+        <v>5.506032031499436</v>
       </c>
       <c r="R38" t="n">
-        <v>3.266140316701616</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>LSC-43</t>
+          <t>LSC-40</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2497922947652635</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D39" t="n">
-        <v>1.708598241528256</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2497922947652635</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G39" t="n">
-        <v>3.6255224140106</v>
+        <v>4.290677160902923</v>
       </c>
       <c r="H39" t="n">
-        <v>4.230308796476028</v>
+        <v>5.454739923312576</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8124108742686269</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J39" t="n">
-        <v>0.2497922947652635</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K39" t="n">
-        <v>2.778232429365308</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M39" t="n">
-        <v>3.711307528786242</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N39" t="n">
-        <v>4.273253579717254</v>
+        <v>3.635588573791124</v>
       </c>
       <c r="O39" t="n">
-        <v>4.708285303808026</v>
+        <v>4.739539537830033</v>
       </c>
       <c r="P39" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.778232429365308</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R39" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.280107919192735</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>LSC-45</t>
+          <t>LSC-41</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2746,16 +2746,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G40" t="n">
-        <v>4.15677962538539</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H40" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I40" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.08037341646402</v>
       </c>
       <c r="J40" t="n">
-        <v>0.5947435215137417</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K40" t="n">
         <v>3.203426503814917e-16</v>
@@ -2767,10 +2767,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N40" t="n">
-        <v>2.192645077942396</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O40" t="n">
-        <v>6.29555811169563</v>
+        <v>5.101538026462062</v>
       </c>
       <c r="P40" t="n">
         <v>3.203426503814917e-16</v>
@@ -2779,17 +2779,17 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R40" t="n">
-        <v>1.339486466271667</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>LSC-53</t>
+          <t>LSC-42</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
         <v>3.203426503814917e-16</v>
@@ -2804,13 +2804,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G41" t="n">
-        <v>3.797347748702223</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H41" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.462819553754064</v>
       </c>
       <c r="I41" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.445799753049531</v>
       </c>
       <c r="J41" t="n">
         <v>3.203426503814917e-16</v>
@@ -2822,86 +2822,86 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M41" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.445799753049531</v>
       </c>
       <c r="N41" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.625834782136685</v>
       </c>
       <c r="O41" t="n">
-        <v>6.434359193595686</v>
+        <v>5.149046271766396</v>
       </c>
       <c r="P41" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.38565369249775</v>
+        <v>2.625834782136685</v>
       </c>
       <c r="R41" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.266140316701616</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LSC-55</t>
+          <t>LSC-43</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5825679855807736</v>
+        <v>0.2497922947652635</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5825679855807736</v>
+        <v>1.708598241528256</v>
       </c>
       <c r="E42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.2497922947652635</v>
       </c>
       <c r="F42" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G42" t="n">
-        <v>4.122499655249576</v>
+        <v>3.6255224140106</v>
       </c>
       <c r="H42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.230308796476028</v>
       </c>
       <c r="I42" t="n">
-        <v>4.037635732043608</v>
+        <v>0.8124108742686269</v>
       </c>
       <c r="J42" t="n">
-        <v>0.9964067352759918</v>
+        <v>0.2497922947652635</v>
       </c>
       <c r="K42" t="n">
-        <v>1.580169489532257</v>
+        <v>2.778232429365308</v>
       </c>
       <c r="L42" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M42" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.711307528786242</v>
       </c>
       <c r="N42" t="n">
-        <v>2.45354706238544</v>
+        <v>4.273253579717254</v>
       </c>
       <c r="O42" t="n">
-        <v>5.774295360253894</v>
+        <v>4.708285303808026</v>
       </c>
       <c r="P42" t="n">
-        <v>1.31761510201628</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.31761510201628</v>
+        <v>2.778232429365308</v>
       </c>
       <c r="R42" t="n">
-        <v>1.994606741229781</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>LSC-56</t>
+          <t>LSC-45</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2920,7 +2920,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G43" t="n">
-        <v>4.612163162004862</v>
+        <v>4.15677962538539</v>
       </c>
       <c r="H43" t="n">
         <v>3.203426503814917e-16</v>
@@ -2929,10 +2929,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J43" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5947435215137417</v>
       </c>
       <c r="K43" t="n">
-        <v>2.411694056204474</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L43" t="n">
         <v>3.203426503814917e-16</v>
@@ -2941,25 +2941,25 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N43" t="n">
-        <v>0.6935729986528256</v>
+        <v>2.192645077942396</v>
       </c>
       <c r="O43" t="n">
-        <v>6.132079184757066</v>
+        <v>6.29555811169563</v>
       </c>
       <c r="P43" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.794576317336301</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R43" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.339486466271667</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>LSC-57</t>
+          <t>LSC-47</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2969,7 +2969,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D44" t="n">
-        <v>3.946466801649578</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E44" t="n">
         <v>3.203426503814917e-16</v>
@@ -2978,19 +2978,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G44" t="n">
-        <v>4.742376604145422</v>
+        <v>2.366007313171981</v>
       </c>
       <c r="H44" t="n">
-        <v>1.341269817188368</v>
+        <v>3.659279427970584</v>
       </c>
       <c r="I44" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6901908350612248</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K44" t="n">
-        <v>1.911015109459704</v>
+        <v>0.6360019337216219</v>
       </c>
       <c r="L44" t="n">
         <v>3.203426503814917e-16</v>
@@ -2999,35 +2999,35 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N44" t="n">
-        <v>3.350844299056191</v>
+        <v>4.462878920255767</v>
       </c>
       <c r="O44" t="n">
-        <v>5.416765153834561</v>
+        <v>5.991042828457422</v>
       </c>
       <c r="P44" t="n">
-        <v>1.654086861375977</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.6901908350612248</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R44" t="n">
-        <v>1.155097583764673</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>LSC-58</t>
+          <t>LSC-48</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4821516951373809</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D45" t="n">
-        <v>2.622632918687211</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E45" t="n">
         <v>3.203426503814917e-16</v>
@@ -3036,19 +3036,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G45" t="n">
-        <v>5.780526748697312</v>
+        <v>3.147876741128932</v>
       </c>
       <c r="H45" t="n">
-        <v>1.757429696725922</v>
+        <v>4.424571275087995</v>
       </c>
       <c r="I45" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.1995849749625519</v>
       </c>
       <c r="J45" t="n">
-        <v>1.757429696725922</v>
+        <v>0.6721734968035544</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8428990389152713</v>
+        <v>1.396185513119206</v>
       </c>
       <c r="L45" t="n">
         <v>3.203426503814917e-16</v>
@@ -3057,32 +3057,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N45" t="n">
-        <v>3.775936825679039</v>
+        <v>5.311940290169167</v>
       </c>
       <c r="O45" t="n">
-        <v>4.435289923305293</v>
+        <v>4.87471233571952</v>
       </c>
       <c r="P45" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.027561507636242</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.4821516951373809</v>
+        <v>0.1995849749625519</v>
       </c>
       <c r="R45" t="n">
-        <v>1.131244533278253</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>LSC-59</t>
+          <t>LSC-53</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5574817642990493</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D46" t="n">
         <v>3.203426503814917e-16</v>
@@ -3094,16 +3094,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G46" t="n">
-        <v>3.623018726983231</v>
+        <v>3.797347748702223</v>
       </c>
       <c r="H46" t="n">
-        <v>5.487612545182457</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3055025469742512</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J46" t="n">
-        <v>1.272079545436801</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K46" t="n">
         <v>3.203426503814917e-16</v>
@@ -3115,16 +3115,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N46" t="n">
-        <v>4.008481476755091</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O46" t="n">
-        <v>4.789256798126342</v>
+        <v>6.434359193595686</v>
       </c>
       <c r="P46" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9585800726200192</v>
+        <v>1.38565369249775</v>
       </c>
       <c r="R46" t="n">
         <v>3.203426503814917e-16</v>
@@ -3133,17 +3133,17 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>LSC-60</t>
+          <t>LSC-55</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>2.813555626621104</v>
+        <v>0.5825679855807736</v>
       </c>
       <c r="D47" t="n">
-        <v>1.812524024831787</v>
+        <v>0.5825679855807736</v>
       </c>
       <c r="E47" t="n">
         <v>3.203426503814917e-16</v>
@@ -3152,19 +3152,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G47" t="n">
-        <v>5.062297041796164</v>
+        <v>4.122499655249576</v>
       </c>
       <c r="H47" t="n">
-        <v>3.328438136200979</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5873770536544561</v>
+        <v>4.037635732043608</v>
       </c>
       <c r="J47" t="n">
-        <v>2.465351050405582</v>
+        <v>0.9964067352759918</v>
       </c>
       <c r="K47" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.580169489532257</v>
       </c>
       <c r="L47" t="n">
         <v>3.203426503814917e-16</v>
@@ -3173,25 +3173,25 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N47" t="n">
-        <v>4.072890040163067</v>
+        <v>2.45354706238544</v>
       </c>
       <c r="O47" t="n">
-        <v>4.801387467107483</v>
+        <v>5.774295360253894</v>
       </c>
       <c r="P47" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.31761510201628</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.70545004745549</v>
+        <v>1.31761510201628</v>
       </c>
       <c r="R47" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.994606741229781</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>LSC-62</t>
+          <t>LSC-56</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -3210,7 +3210,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G48" t="n">
-        <v>5.884219765410462</v>
+        <v>4.612163162004862</v>
       </c>
       <c r="H48" t="n">
         <v>3.203426503814917e-16</v>
@@ -3222,7 +3222,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K48" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.411694056204474</v>
       </c>
       <c r="L48" t="n">
         <v>3.203426503814917e-16</v>
@@ -3231,16 +3231,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N48" t="n">
-        <v>3.797347748702223</v>
+        <v>0.6935729986528256</v>
       </c>
       <c r="O48" t="n">
-        <v>4.908441047171919</v>
+        <v>6.132079184757066</v>
       </c>
       <c r="P48" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.794576317336301</v>
       </c>
       <c r="R48" t="n">
         <v>3.203426503814917e-16</v>
@@ -3249,17 +3249,17 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>SCR-08</t>
+          <t>LSC-57</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>1.349358265727701</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D49" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.946466801649578</v>
       </c>
       <c r="E49" t="n">
         <v>3.203426503814917e-16</v>
@@ -3268,56 +3268,56 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G49" t="n">
-        <v>4.616440732194325</v>
+        <v>4.742376604145422</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3891234984260248</v>
+        <v>1.341269817188368</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6952767815530165</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J49" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6901908350612248</v>
       </c>
       <c r="K49" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.911015109459704</v>
       </c>
       <c r="L49" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M49" t="n">
-        <v>0.3891234984260248</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N49" t="n">
-        <v>1.514796482951849</v>
+        <v>3.350844299056191</v>
       </c>
       <c r="O49" t="n">
-        <v>6.167876379727164</v>
+        <v>5.416765153834561</v>
       </c>
       <c r="P49" t="n">
-        <v>0.9476979983300771</v>
+        <v>1.654086861375977</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.6901908350612248</v>
       </c>
       <c r="R49" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.155097583764673</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>DR-144</t>
+          <t>LSC-58</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>1.330645311988472</v>
+        <v>0.4821516951373809</v>
       </c>
       <c r="D50" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.622632918687211</v>
       </c>
       <c r="E50" t="n">
         <v>3.203426503814917e-16</v>
@@ -3326,19 +3326,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G50" t="n">
-        <v>5.872231802852783</v>
+        <v>5.780526748697312</v>
       </c>
       <c r="H50" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.757429696725922</v>
       </c>
       <c r="I50" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J50" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.757429696725922</v>
       </c>
       <c r="K50" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8428990389152713</v>
       </c>
       <c r="L50" t="n">
         <v>3.203426503814917e-16</v>
@@ -3347,74 +3347,74 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N50" t="n">
-        <v>3.87148525947732</v>
+        <v>3.775936825679039</v>
       </c>
       <c r="O50" t="n">
-        <v>4.741875508290013</v>
+        <v>4.435289923305293</v>
       </c>
       <c r="P50" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.330645311988472</v>
+        <v>0.4821516951373809</v>
       </c>
       <c r="R50" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.131244533278253</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>DR-145</t>
+          <t>LSC-59</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="n">
+        <v>0.5574817642990493</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3.623018726983231</v>
+      </c>
+      <c r="H51" t="n">
+        <v>5.487612545182457</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.3055025469742512</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.272079545436801</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4.008481476755091</v>
+      </c>
+      <c r="O51" t="n">
+        <v>4.789256798126342</v>
+      </c>
+      <c r="P51" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q51" t="n">
         <v>0.9585800726200192</v>
-      </c>
-      <c r="D51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G51" t="n">
-        <v>4.312369266462518</v>
-      </c>
-      <c r="H51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L51" t="n">
-        <v>2.515253528909752</v>
-      </c>
-      <c r="M51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4.090661722917659</v>
-      </c>
-      <c r="O51" t="n">
-        <v>5.917287628211485</v>
-      </c>
-      <c r="P51" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>3.203426503814917e-16</v>
       </c>
       <c r="R51" t="n">
         <v>3.203426503814917e-16</v>
@@ -3423,17 +3423,17 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>SCR-09</t>
+          <t>LSC-60</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.813555626621104</v>
       </c>
       <c r="D52" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.812524024831787</v>
       </c>
       <c r="E52" t="n">
         <v>3.203426503814917e-16</v>
@@ -3442,37 +3442,37 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G52" t="n">
-        <v>5.3375904957025</v>
+        <v>5.062297041796164</v>
       </c>
       <c r="H52" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.328438136200979</v>
       </c>
       <c r="I52" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5873770536544561</v>
       </c>
       <c r="J52" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.465351050405582</v>
       </c>
       <c r="K52" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L52" t="n">
-        <v>2.385528257116121</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M52" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N52" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.072890040163067</v>
       </c>
       <c r="O52" t="n">
-        <v>5.768743472787629</v>
+        <v>4.801387467107483</v>
       </c>
       <c r="P52" t="n">
-        <v>1.268105395381216</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.268105395381216</v>
+        <v>1.70545004745549</v>
       </c>
       <c r="R52" t="n">
         <v>3.203426503814917e-16</v>
@@ -3481,58 +3481,464 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
+          <t>LSC-62</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5.884219765410462</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3.797347748702223</v>
+      </c>
+      <c r="O53" t="n">
+        <v>4.908441047171919</v>
+      </c>
+      <c r="P53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="R53" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SCR-08</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1.349358265727701</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4.616440732194325</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.3891234984260248</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.6952767815530165</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.3891234984260248</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1.514796482951849</v>
+      </c>
+      <c r="O54" t="n">
+        <v>6.167876379727164</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.9476979983300771</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="R54" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>DR-144</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1.330645311988472</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5.872231802852783</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3.87148525947732</v>
+      </c>
+      <c r="O55" t="n">
+        <v>4.741875508290013</v>
+      </c>
+      <c r="P55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.330645311988472</v>
+      </c>
+      <c r="R55" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>DR-145</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.9585800726200192</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G56" t="n">
+        <v>4.312369266462518</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2.515253528909752</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N56" t="n">
+        <v>4.090661722917659</v>
+      </c>
+      <c r="O56" t="n">
+        <v>5.917287628211485</v>
+      </c>
+      <c r="P56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="R56" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SCR-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5.3375904957025</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L57" t="n">
+        <v>2.385528257116121</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="O57" t="n">
+        <v>5.768743472787629</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.268105395381216</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.268105395381216</v>
+      </c>
+      <c r="R57" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>DR-156</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5.317915032380739</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.598259323334614</v>
+      </c>
+      <c r="O58" t="n">
+        <v>5.672425341971495</v>
+      </c>
+      <c r="P58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="R58" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>DR-157</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1.34845438939755</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.5997595026492368</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3.038523071803344</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3.126305317145071</v>
+      </c>
+      <c r="O59" t="n">
+        <v>6.203209230748278</v>
+      </c>
+      <c r="P59" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>3.126305317145071</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.838879010391133</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
           <t>DR-159</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="D53" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E53" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F53" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G53" t="n">
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="D60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G60" t="n">
         <v>2.493040011280117</v>
       </c>
-      <c r="H53" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I53" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J53" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K53" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L53" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M53" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N53" t="n">
+      <c r="H60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N60" t="n">
         <v>2.233797184608697</v>
       </c>
-      <c r="O53" t="n">
+      <c r="O60" t="n">
         <v>6.533978572002351</v>
       </c>
-      <c r="P53" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="R53" t="n">
+      <c r="P60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="R60" t="n">
         <v>3.203426503814917e-16</v>
       </c>
     </row>
